--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Agra-Trucking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A81C3A-B891-47B5-A3E6-3A67805F45D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8728FFC-4F24-41F4-907E-B8E80B76A524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1215" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="58">
   <si>
     <t>Company Name</t>
   </si>
@@ -86,9 +86,6 @@
     <t>UNKNOWN</t>
   </si>
   <si>
-    <t>Scene of an Accident</t>
-  </si>
-  <si>
     <t>Speed Management</t>
   </si>
   <si>
@@ -116,16 +113,10 @@
     <t>Driver Health</t>
   </si>
   <si>
-    <t>Dangers of Aggressive Driving for CMV Drivers</t>
-  </si>
-  <si>
     <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Mark Complete</t>
-  </si>
-  <si>
-    <t>Camera Event Management (Onboarding)</t>
   </si>
   <si>
     <t>Fire Extinguisher Training for CDL</t>
@@ -134,52 +125,94 @@
     <t>Alert Driving: Big Three</t>
   </si>
   <si>
-    <t>Camera Event Management Orientation for Drivers</t>
-  </si>
-  <si>
     <t>Space Management for Commercial Vehicles</t>
   </si>
   <si>
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>Alandon Tow Service</t>
+    <t>Agra Trucking</t>
   </si>
   <si>
-    <t>Daniel King</t>
+    <t>Alvaro Rodriguez</t>
   </si>
   <si>
-    <t>Dustin Porter</t>
+    <t>DNU-Driver Health</t>
   </si>
   <si>
-    <t>Joseph Pierce</t>
+    <t>George Benjamin</t>
   </si>
   <si>
-    <t>Keyden Berry</t>
+    <t>Jose Vargas</t>
   </si>
   <si>
-    <t>Mason Douglas</t>
+    <t>Martin Alverez</t>
   </si>
   <si>
-    <t>Michael Roberts</t>
+    <t>Seth Trout</t>
   </si>
   <si>
-    <t>Billy Sickman</t>
+    <t>DNU-Scene of an Accident</t>
   </si>
   <si>
-    <t>Vincent Williams</t>
+    <t>DNU-NEW-Vehicle Inspections</t>
   </si>
   <si>
-    <t>William Davis</t>
+    <t>Javier Quintana</t>
   </si>
   <si>
-    <t>Demetrius Palmer</t>
+    <t>Michael Moreno</t>
   </si>
   <si>
-    <t>Eugene Allen Edward</t>
+    <t>Miguel Ochoa</t>
   </si>
   <si>
-    <t>Austin Simms</t>
+    <t>Sergio Villalobos</t>
+  </si>
+  <si>
+    <t>Timothy Harmening</t>
+  </si>
+  <si>
+    <t>Backing Commercial Vehicles</t>
+  </si>
+  <si>
+    <t>Daniel Serrano Carrillo</t>
+  </si>
+  <si>
+    <t>Lino Ortega</t>
+  </si>
+  <si>
+    <t>Parmjit Singh</t>
+  </si>
+  <si>
+    <t>Work Zone Safety</t>
+  </si>
+  <si>
+    <t>Eric Vazquez</t>
+  </si>
+  <si>
+    <t>Ignacio Angelo Oserguera Mendoza</t>
+  </si>
+  <si>
+    <t>Fatigue</t>
+  </si>
+  <si>
+    <t>Micro-Learn Speed</t>
+  </si>
+  <si>
+    <t>Micro-Learn Space Mangement</t>
+  </si>
+  <si>
+    <t>Salomon Aguilar</t>
+  </si>
+  <si>
+    <t>Hector Antonio Medina</t>
+  </si>
+  <si>
+    <t>Jacinto Villalpando Jr Silvia</t>
+  </si>
+  <si>
+    <t>Safe Lifting for Commercial Drivers</t>
   </si>
 </sst>
 </file>
@@ -601,25 +634,25 @@
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C2">
-        <v>2826</v>
+        <v>1841</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="2">
-        <v>1.6041666666666666E-2</v>
+        <v>2.4710648148148148E-2</v>
       </c>
       <c r="I2" s="1">
-        <v>45600.867465277777</v>
+        <v>45446.61377314815</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -630,25 +663,25 @@
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C3">
-        <v>2828</v>
+        <v>1843</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H3" s="2">
-        <v>1.3321759259259259E-2</v>
+        <v>1.7395833333333333E-2</v>
       </c>
       <c r="I3" s="1">
-        <v>45600.867465277777</v>
+        <v>45446.61377314815</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -659,86 +692,66 @@
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4">
+        <v>1840</v>
+      </c>
+      <c r="D4" t="s">
         <v>34</v>
       </c>
-      <c r="C4">
-        <v>2830</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H4" s="2">
-        <v>9.5833333333333326E-3</v>
+        <v>8.262731481481482E-2</v>
       </c>
       <c r="I4" s="1">
-        <v>45600.867465277777</v>
+        <v>45446.61377314815</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5">
-        <v>2829</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1.1458333333333333E-2</v>
-      </c>
-      <c r="I5" s="1">
-        <v>45600.867465277777</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="1"/>
       <c r="K5" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C6">
-        <v>2832</v>
+        <v>1842</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H6" s="2">
-        <v>1.0300925925925925E-2</v>
+        <v>1.0555555555555556E-2</v>
       </c>
       <c r="I6" s="1">
-        <v>45600.867465277777</v>
+        <v>45446.61377314815</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="s">
         <v>11</v>
@@ -746,25 +759,25 @@
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C7">
-        <v>2825</v>
+        <v>1839</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H7" s="2">
-        <v>6.7129629629629631E-3</v>
+        <v>1.4085648148148147E-2</v>
       </c>
       <c r="I7" s="1">
-        <v>45600.867465277777</v>
+        <v>45446.61377314815</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -775,25 +788,25 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>2919</v>
+        <v>1841</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H8" s="2">
-        <v>8.9120370370370378E-3</v>
+        <v>4.8680555555555553E-2</v>
       </c>
       <c r="I8" s="1">
-        <v>45628.829606481479</v>
+        <v>45474.709247685183</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -803,58 +816,38 @@
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9">
-        <v>2826</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="2">
-        <v>5.7407407407407407E-3</v>
-      </c>
-      <c r="I9" s="1">
-        <v>45628.829606481479</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="1"/>
       <c r="K9" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C10">
-        <v>2828</v>
+        <v>1843</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H10" s="2">
-        <v>5.7407407407407407E-3</v>
+        <v>1.7881944444444443E-2</v>
       </c>
       <c r="I10" s="1">
-        <v>45628.829606481479</v>
+        <v>45474.709247685183</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="s">
         <v>11</v>
@@ -862,28 +855,28 @@
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11">
+        <v>1840</v>
+      </c>
+      <c r="D11" t="s">
         <v>34</v>
       </c>
-      <c r="C11">
-        <v>2830</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="F11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="G11" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H11" s="2">
-        <v>2.1087962962962965E-2</v>
+        <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>45628.829606481479</v>
+        <v>45474.709247685183</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="s">
         <v>11</v>
@@ -891,28 +884,28 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C12">
-        <v>2829</v>
+        <v>1842</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H12" s="2">
-        <v>7.3379629629629628E-3</v>
+        <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>45628.829606481479</v>
+        <v>45474.709247685183</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="s">
         <v>11</v>
@@ -920,28 +913,28 @@
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C13">
-        <v>2832</v>
+        <v>1839</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H13" s="2">
-        <v>7.4537037037037037E-3</v>
+        <v>3.5300925925925923E-2</v>
       </c>
       <c r="I13" s="1">
-        <v>45628.829606481479</v>
+        <v>45474.709247685183</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13" t="s">
         <v>11</v>
@@ -949,28 +942,28 @@
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C14">
-        <v>2825</v>
+        <v>1841</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H14" s="2">
-        <v>5.185185185185185E-3</v>
+        <v>2.0219907407407409E-2</v>
       </c>
       <c r="I14" s="1">
-        <v>45628.829606481479</v>
+        <v>45509.49900462963</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="s">
         <v>11</v>
@@ -978,124 +971,124 @@
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C15">
-        <v>2919</v>
+        <v>1843</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H15" s="2">
-        <v>2.3148148148148147E-5</v>
+        <v>0</v>
       </c>
       <c r="I15" s="1">
-        <v>45663.46261574074</v>
+        <v>45509.49900462963</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K15" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F16" s="2"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="1"/>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16">
+        <v>2008</v>
+      </c>
+      <c r="D16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="2">
+        <v>7.7546296296296295E-3</v>
+      </c>
+      <c r="I16" s="1">
+        <v>45509.49900462963</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
       <c r="K16" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17">
+        <v>1840</v>
+      </c>
+      <c r="D17" t="s">
         <v>34</v>
       </c>
-      <c r="C17">
-        <v>2826</v>
-      </c>
-      <c r="D17" t="s">
-        <v>35</v>
-      </c>
       <c r="F17" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2">
-        <v>8.5648148148148154E-2</v>
+        <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>45663.46261574074</v>
+        <v>45509.49900462963</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18">
-        <v>2828</v>
-      </c>
-      <c r="D18" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H18" s="2">
-        <v>1.0231481481481482E-2</v>
-      </c>
-      <c r="I18" s="1">
-        <v>45663.46261574074</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="1"/>
       <c r="K18" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C19">
-        <v>2830</v>
+        <v>1842</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H19" s="2">
-        <v>0.20502314814814815</v>
+        <v>0</v>
       </c>
       <c r="I19" s="1">
-        <v>45663.463310185187</v>
+        <v>45509.49900462963</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="s">
         <v>11</v>
@@ -1103,25 +1096,25 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C20">
-        <v>2829</v>
+        <v>2027</v>
       </c>
       <c r="D20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H20" s="2">
-        <v>1.1469907407407408E-2</v>
+        <v>6.806712962962963E-2</v>
       </c>
       <c r="I20" s="1">
-        <v>45663.463310185187</v>
+        <v>45509.49900462963</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1132,28 +1125,28 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C21">
-        <v>2832</v>
+        <v>2043</v>
       </c>
       <c r="D21" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H21" s="2">
-        <v>3.3564814814814816E-3</v>
+        <v>0</v>
       </c>
       <c r="I21" s="1">
-        <v>45663.463310185187</v>
+        <v>45509.49900462963</v>
       </c>
       <c r="J21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K21" t="s">
         <v>11</v>
@@ -1164,33 +1157,33 @@
       <c r="G22" s="1"/>
       <c r="I22" s="1"/>
       <c r="K22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C23">
-        <v>2825</v>
+        <v>2007</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H23" s="2">
-        <v>1.0868055555555556E-2</v>
+        <v>0.10136574074074074</v>
       </c>
       <c r="I23" s="1">
-        <v>45663.464004629626</v>
+        <v>45509.49900462963</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="s">
         <v>11</v>
@@ -1198,109 +1191,109 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C24">
-        <v>3009</v>
+        <v>1839</v>
       </c>
       <c r="D24" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H24" s="2">
-        <v>1.8912037037037036E-2</v>
+        <v>2.0370370370370369E-3</v>
       </c>
       <c r="I24" s="1">
-        <v>45663.464004629626</v>
+        <v>45509.49900462963</v>
       </c>
       <c r="J24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25">
-        <v>2919</v>
-      </c>
-      <c r="D25" t="s">
-        <v>41</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H25" s="2">
-        <v>1.3819444444444445E-2</v>
-      </c>
-      <c r="I25" s="1">
-        <v>45691.630324074074</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="1"/>
       <c r="K25" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C26">
-        <v>2826</v>
+        <v>2009</v>
       </c>
       <c r="D26" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H26" s="2">
-        <v>6.9444444444444444E-5</v>
+        <v>6.3541666666666668E-3</v>
       </c>
       <c r="I26" s="1">
-        <v>45691.630324074074</v>
+        <v>45509.49900462963</v>
       </c>
       <c r="J26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F27" s="2"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="1"/>
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27">
+        <v>1843</v>
+      </c>
+      <c r="D27" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="2">
+        <v>1.1261574074074075E-2</v>
+      </c>
+      <c r="I27" s="1">
+        <v>45523.547476851854</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
       <c r="K27" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28">
+        <v>1840</v>
+      </c>
+      <c r="D28" t="s">
         <v>34</v>
-      </c>
-      <c r="C28">
-        <v>2828</v>
-      </c>
-      <c r="D28" t="s">
-        <v>36</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>16</v>
@@ -1309,13 +1302,13 @@
         <v>10</v>
       </c>
       <c r="H28" s="2">
-        <v>7.5462962962962966E-3</v>
+        <v>2.1111111111111112E-2</v>
       </c>
       <c r="I28" s="1">
-        <v>45691.631018518521</v>
+        <v>45523.547476851854</v>
       </c>
       <c r="J28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K28" t="s">
         <v>11</v>
@@ -1323,28 +1316,28 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C29">
-        <v>2830</v>
+        <v>1842</v>
       </c>
       <c r="D29" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H29" s="2">
-        <v>9.1435185185185178E-3</v>
+        <v>0</v>
       </c>
       <c r="I29" s="1">
-        <v>45691.631018518521</v>
+        <v>45523.547476851854</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="s">
         <v>11</v>
@@ -1352,71 +1345,51 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C30">
-        <v>2829</v>
+        <v>2043</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H30" s="2">
-        <v>9.4560185185185181E-3</v>
+        <v>4.6296296296296294E-5</v>
       </c>
       <c r="I30" s="1">
-        <v>45691.631018518521</v>
+        <v>45523.547476851854</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31">
-        <v>2832</v>
-      </c>
-      <c r="D31" t="s">
-        <v>39</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H31" s="2">
-        <v>8.0555555555555554E-3</v>
-      </c>
-      <c r="I31" s="1">
-        <v>45691.631712962961</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="1"/>
       <c r="K31" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C32">
-        <v>2825</v>
+        <v>1839</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>16</v>
@@ -1425,13 +1398,13 @@
         <v>10</v>
       </c>
       <c r="H32" s="2">
-        <v>7.2453703703703708E-3</v>
+        <v>5.5092592592592589E-3</v>
       </c>
       <c r="I32" s="1">
-        <v>45691.631712962961</v>
+        <v>45523.547476851854</v>
       </c>
       <c r="J32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K32" t="s">
         <v>11</v>
@@ -1439,28 +1412,28 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C33">
-        <v>3009</v>
+        <v>1841</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H33" s="2">
+        <v>1.7106481481481483E-2</v>
+      </c>
+      <c r="I33" s="1">
+        <v>45538.599270833336</v>
+      </c>
+      <c r="J33">
         <v>0</v>
-      </c>
-      <c r="I33" s="1">
-        <v>45691.632407407407</v>
-      </c>
-      <c r="J33">
-        <v>3</v>
       </c>
       <c r="K33" t="s">
         <v>11</v>
@@ -1468,63 +1441,83 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C34">
-        <v>2827</v>
+        <v>2270</v>
       </c>
       <c r="D34" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H34" s="2">
-        <v>1.8981481481481482E-3</v>
+        <v>5.8101851851851856E-3</v>
       </c>
       <c r="I34" s="1">
-        <v>45691.632407407407</v>
+        <v>45538.599270833336</v>
       </c>
       <c r="J34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K34" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F35" s="2"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="1"/>
+      <c r="B35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35">
+        <v>1843</v>
+      </c>
+      <c r="D35" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="2">
+        <v>1.0902777777777779E-2</v>
+      </c>
+      <c r="I35" s="1">
+        <v>45538.599270833336</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
       <c r="K35" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C36">
-        <v>2919</v>
+        <v>2008</v>
       </c>
       <c r="D36" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H36" s="2">
-        <v>1.255787037037037E-2</v>
+        <v>6.2384259259259259E-3</v>
       </c>
       <c r="I36" s="1">
-        <v>45719.62939814815</v>
+        <v>45538.599270833336</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -1535,28 +1528,28 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37">
+        <v>1840</v>
+      </c>
+      <c r="D37" t="s">
         <v>34</v>
       </c>
-      <c r="C37">
-        <v>2826</v>
-      </c>
-      <c r="D37" t="s">
-        <v>35</v>
-      </c>
       <c r="F37" s="2" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H37" s="2">
-        <v>0.19252314814814814</v>
+        <v>2.6574074074074073E-2</v>
       </c>
       <c r="I37" s="1">
-        <v>45719.62939814815</v>
+        <v>45538.599270833336</v>
       </c>
       <c r="J37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K37" t="s">
         <v>11</v>
@@ -1564,86 +1557,66 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C38">
-        <v>2828</v>
+        <v>2269</v>
       </c>
       <c r="D38" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H38" s="2">
-        <v>8.2986111111111108E-3</v>
+        <v>0</v>
       </c>
       <c r="I38" s="1">
-        <v>45719.63009259259</v>
+        <v>45538.599270833336</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K38" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39">
-        <v>2830</v>
-      </c>
-      <c r="D39" t="s">
-        <v>37</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H39" s="2">
-        <v>9.9537037037037042E-3</v>
-      </c>
-      <c r="I39" s="1">
-        <v>45719.630787037036</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="1"/>
       <c r="K39" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C40">
-        <v>2829</v>
+        <v>1842</v>
       </c>
       <c r="D40" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H40" s="2">
-        <v>7.9745370370370369E-3</v>
+        <v>0</v>
       </c>
       <c r="I40" s="1">
-        <v>45719.630787037036</v>
+        <v>45538.599270833336</v>
       </c>
       <c r="J40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K40" t="s">
         <v>11</v>
@@ -1651,28 +1624,28 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C41">
-        <v>2832</v>
+        <v>2043</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H41" s="2">
-        <v>7.9976851851851858E-3</v>
+        <v>0</v>
       </c>
       <c r="I41" s="1">
-        <v>45719.630787037036</v>
+        <v>45538.599270833336</v>
       </c>
       <c r="J41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K41" t="s">
         <v>11</v>
@@ -1680,28 +1653,28 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C42">
-        <v>2825</v>
+        <v>2275</v>
       </c>
       <c r="D42" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H42" s="2">
+        <v>4.4212962962962964E-3</v>
+      </c>
+      <c r="I42" s="1">
+        <v>45538.599270833336</v>
+      </c>
+      <c r="J42">
         <v>0</v>
-      </c>
-      <c r="I42" s="1">
-        <v>45719.631481481483</v>
-      </c>
-      <c r="J42">
-        <v>3</v>
       </c>
       <c r="K42" t="s">
         <v>11</v>
@@ -1709,28 +1682,28 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C43">
-        <v>3009</v>
+        <v>1839</v>
       </c>
       <c r="D43" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H43" s="2">
+        <v>5.7986111111111112E-3</v>
+      </c>
+      <c r="I43" s="1">
+        <v>45538.599270833336</v>
+      </c>
+      <c r="J43">
         <v>0</v>
-      </c>
-      <c r="I43" s="1">
-        <v>45719.631481481483</v>
-      </c>
-      <c r="J43">
-        <v>3</v>
       </c>
       <c r="K43" t="s">
         <v>11</v>
@@ -1738,28 +1711,28 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C44">
-        <v>2827</v>
+        <v>2009</v>
       </c>
       <c r="D44" t="s">
         <v>43</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H44" s="2">
-        <v>1.0578703703703703E-2</v>
+        <v>0</v>
       </c>
       <c r="I44" s="1">
-        <v>45719.632175925923</v>
+        <v>45538.599270833336</v>
       </c>
       <c r="J44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K44" t="s">
         <v>11</v>
@@ -1767,28 +1740,28 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C45">
-        <v>2919</v>
+        <v>1841</v>
       </c>
       <c r="D45" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H45" s="2">
-        <v>0</v>
+        <v>1.4664351851851852E-2</v>
       </c>
       <c r="I45" s="1">
-        <v>45754.71365740741</v>
+        <v>45572.626296296294</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="s">
         <v>11</v>
@@ -1796,28 +1769,28 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C46">
-        <v>2826</v>
+        <v>2270</v>
       </c>
       <c r="D46" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H46" s="2">
-        <v>6.1574074074074074E-3</v>
+        <v>0</v>
       </c>
       <c r="I46" s="1">
-        <v>45754.71435185185</v>
+        <v>45572.626296296294</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K46" t="s">
         <v>11</v>
@@ -1825,28 +1798,28 @@
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C47">
-        <v>2828</v>
+        <v>2714</v>
       </c>
       <c r="D47" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H47" s="2">
-        <v>6.3425925925925924E-3</v>
+        <v>0</v>
       </c>
       <c r="I47" s="1">
-        <v>45754.715046296296</v>
+        <v>45572.626296296294</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K47" t="s">
         <v>11</v>
@@ -1854,86 +1827,66 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C48">
-        <v>2830</v>
+        <v>1843</v>
       </c>
       <c r="D48" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H48" s="2">
-        <v>5.5671296296296293E-3</v>
+        <v>5.0810185185185186E-3</v>
       </c>
       <c r="I48" s="1">
-        <v>45754.715046296296</v>
+        <v>45572.626296296294</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K48" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
-        <v>34</v>
-      </c>
-      <c r="C49">
-        <v>2829</v>
-      </c>
-      <c r="D49" t="s">
-        <v>38</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H49" s="2">
-        <v>7.5115740740740742E-3</v>
-      </c>
-      <c r="I49" s="1">
-        <v>45754.715740740743</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
+      <c r="F49" s="2"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="1"/>
       <c r="K49" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C50">
-        <v>2832</v>
+        <v>2512</v>
       </c>
       <c r="D50" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H50" s="2">
-        <v>6.1689814814814819E-3</v>
+        <v>0</v>
       </c>
       <c r="I50" s="1">
-        <v>45754.716435185182</v>
+        <v>45572.626296296294</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K50" t="s">
         <v>11</v>
@@ -1941,25 +1894,25 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C51">
-        <v>2825</v>
+        <v>2008</v>
       </c>
       <c r="D51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H51" s="2">
-        <v>6.7013888888888887E-3</v>
+        <v>1.1377314814814814E-2</v>
       </c>
       <c r="I51" s="1">
-        <v>45754.716435185182</v>
+        <v>45572.626296296294</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -1970,28 +1923,28 @@
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52">
+        <v>1840</v>
+      </c>
+      <c r="D52" t="s">
         <v>34</v>
       </c>
-      <c r="C52">
-        <v>3009</v>
-      </c>
-      <c r="D52" t="s">
-        <v>42</v>
-      </c>
       <c r="F52" s="2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H52" s="2">
-        <v>1.0023148148148147E-2</v>
+        <v>1.1018518518518518E-2</v>
       </c>
       <c r="I52" s="1">
-        <v>45754.717129629629</v>
+        <v>45572.626296296294</v>
       </c>
       <c r="J52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K52" t="s">
         <v>11</v>
@@ -1999,25 +1952,25 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C53">
-        <v>2827</v>
+        <v>1842</v>
       </c>
       <c r="D53" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H53">
         <v>0</v>
       </c>
       <c r="I53" s="1">
-        <v>45754.717824074076</v>
+        <v>45572.626296296294</v>
       </c>
       <c r="J53">
         <v>3</v>
@@ -2027,35 +1980,55 @@
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F54" s="2"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="1"/>
+      <c r="B54" t="s">
+        <v>30</v>
+      </c>
+      <c r="C54">
+        <v>2043</v>
+      </c>
+      <c r="D54" t="s">
+        <v>41</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" s="2">
+        <v>0</v>
+      </c>
+      <c r="I54" s="1">
+        <v>45572.626296296294</v>
+      </c>
+      <c r="J54">
+        <v>3</v>
+      </c>
       <c r="K54" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C55">
-        <v>2919</v>
+        <v>1839</v>
       </c>
       <c r="D55" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H55" s="2">
-        <v>9.8842592592592593E-3</v>
+        <v>7.4305555555555557E-3</v>
       </c>
       <c r="I55" s="1">
-        <v>45782.629629629628</v>
+        <v>45572.626296296294</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -2066,28 +2039,28 @@
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C56">
-        <v>2826</v>
+        <v>2009</v>
       </c>
       <c r="D56" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H56" s="2">
-        <v>1.0671296296296297E-2</v>
+        <v>0</v>
       </c>
       <c r="I56" s="1">
-        <v>45782.629629629628</v>
+        <v>45572.626296296294</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K56" t="s">
         <v>11</v>
@@ -2095,28 +2068,28 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C57">
-        <v>2828</v>
+        <v>1841</v>
       </c>
       <c r="D57" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H57" s="2">
-        <v>1.4606481481481481E-2</v>
+        <v>1.4583333333333334E-2</v>
       </c>
       <c r="I57" s="1">
-        <v>45782.630324074074</v>
+        <v>45600.849409722221</v>
       </c>
       <c r="J57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="s">
         <v>11</v>
@@ -2124,28 +2097,28 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C58">
-        <v>2830</v>
+        <v>2270</v>
       </c>
       <c r="D58" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H58" s="2">
-        <v>1.5277777777777777E-2</v>
+        <v>0</v>
       </c>
       <c r="I58" s="1">
-        <v>45782.630324074074</v>
+        <v>45600.849409722221</v>
       </c>
       <c r="J58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K58" t="s">
         <v>11</v>
@@ -2153,28 +2126,28 @@
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C59">
-        <v>2829</v>
+        <v>2714</v>
       </c>
       <c r="D59" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H59" s="2">
-        <v>1.0543981481481482E-2</v>
+        <v>0</v>
       </c>
       <c r="I59" s="1">
-        <v>45782.631018518521</v>
+        <v>45600.849409722221</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K59" t="s">
         <v>11</v>
@@ -2182,28 +2155,28 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C60">
-        <v>2832</v>
+        <v>1843</v>
       </c>
       <c r="D60" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H60" s="2">
-        <v>9.4212962962962957E-3</v>
+        <v>0</v>
       </c>
       <c r="I60" s="1">
-        <v>45782.631018518521</v>
+        <v>45600.849409722221</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K60" t="s">
         <v>11</v>
@@ -2211,25 +2184,25 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C61">
-        <v>2825</v>
+        <v>2512</v>
       </c>
       <c r="D61" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H61" s="2">
-        <v>7.6736111111111111E-3</v>
+        <v>0</v>
       </c>
       <c r="I61" s="1">
-        <v>45782.631712962961</v>
+        <v>45600.849409722221</v>
       </c>
       <c r="J61">
         <v>2</v>
@@ -2240,28 +2213,28 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C62">
-        <v>2827</v>
+        <v>2008</v>
       </c>
       <c r="D62" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H62" s="2">
+        <v>9.6990740740740735E-3</v>
+      </c>
+      <c r="I62" s="1">
+        <v>45600.849409722221</v>
+      </c>
+      <c r="J62">
         <v>0</v>
-      </c>
-      <c r="I62" s="1">
-        <v>45782.631712962961</v>
-      </c>
-      <c r="J62">
-        <v>3</v>
       </c>
       <c r="K62" t="s">
         <v>11</v>
@@ -2269,28 +2242,28 @@
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63">
+        <v>1840</v>
+      </c>
+      <c r="D63" t="s">
         <v>34</v>
       </c>
-      <c r="C63">
-        <v>2919</v>
-      </c>
-      <c r="D63" t="s">
-        <v>41</v>
-      </c>
       <c r="F63" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H63" s="2">
-        <v>6.9918981481481485E-2</v>
+        <v>1.1284722222222222E-2</v>
       </c>
       <c r="I63" s="1">
-        <v>45810.670949074076</v>
+        <v>45600.849409722221</v>
       </c>
       <c r="J63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="s">
         <v>11</v>
@@ -2298,28 +2271,28 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C64">
-        <v>2826</v>
+        <v>1842</v>
       </c>
       <c r="D64" t="s">
         <v>35</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H64" s="2">
-        <v>1.6527777777777777E-2</v>
+        <v>0</v>
       </c>
       <c r="I64" s="1">
-        <v>45810.671643518515</v>
+        <v>45600.849409722221</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K64" t="s">
         <v>11</v>
@@ -2327,28 +2300,28 @@
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C65">
-        <v>3666</v>
+        <v>2043</v>
       </c>
       <c r="D65" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H65" s="2">
-        <v>1.292824074074074E-2</v>
+        <v>0</v>
       </c>
       <c r="I65" s="1">
-        <v>45810.672337962962</v>
+        <v>45600.849409722221</v>
       </c>
       <c r="J65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K65" t="s">
         <v>11</v>
@@ -2356,28 +2329,28 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C66">
-        <v>2828</v>
+        <v>1839</v>
       </c>
       <c r="D66" t="s">
         <v>36</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H66" s="2">
-        <v>8.0787037037037043E-3</v>
+        <v>1.5891203703703703E-2</v>
       </c>
       <c r="I66" s="1">
-        <v>45810.672337962962</v>
+        <v>45600.849409722221</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="s">
         <v>11</v>
@@ -2385,28 +2358,28 @@
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C67">
-        <v>2830</v>
+        <v>2009</v>
       </c>
       <c r="D67" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H67" s="2">
-        <v>8.6574074074074071E-3</v>
+        <v>0</v>
       </c>
       <c r="I67" s="1">
-        <v>45810.673032407409</v>
+        <v>45600.849409722221</v>
       </c>
       <c r="J67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K67" t="s">
         <v>11</v>
@@ -2414,25 +2387,25 @@
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C68">
-        <v>2829</v>
+        <v>1841</v>
       </c>
       <c r="D68" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H68" s="2">
-        <v>3.3750000000000002E-2</v>
+        <v>1.2800925925925926E-2</v>
       </c>
       <c r="I68" s="1">
-        <v>45810.673032407409</v>
+        <v>45628.821967592594</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -2443,28 +2416,28 @@
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C69">
-        <v>2832</v>
+        <v>2270</v>
       </c>
       <c r="D69" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H69" s="2">
-        <v>8.0555555555555554E-3</v>
+        <v>5.1504629629629626E-3</v>
       </c>
       <c r="I69" s="1">
-        <v>45810.673726851855</v>
+        <v>45628.821967592594</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="s">
         <v>11</v>
@@ -2472,28 +2445,28 @@
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C70">
-        <v>2825</v>
+        <v>2714</v>
       </c>
       <c r="D70" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H70" s="2">
-        <v>0</v>
+        <v>8.4837962962962966E-3</v>
       </c>
       <c r="I70" s="1">
-        <v>45810.673726851855</v>
+        <v>45628.821967592594</v>
       </c>
       <c r="J70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K70" t="s">
         <v>11</v>
@@ -2501,28 +2474,28 @@
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C71">
-        <v>2827</v>
+        <v>1843</v>
       </c>
       <c r="D71" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H71" s="2">
-        <v>2.0347222222222221E-2</v>
+        <v>1.0891203703703703E-2</v>
       </c>
       <c r="I71" s="1">
-        <v>45810.674421296295</v>
+        <v>45628.821967592594</v>
       </c>
       <c r="J71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K71" t="s">
         <v>11</v>
@@ -2530,28 +2503,28 @@
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
+        <v>30</v>
+      </c>
+      <c r="C72">
+        <v>1840</v>
+      </c>
+      <c r="D72" t="s">
         <v>34</v>
       </c>
-      <c r="C72">
-        <v>2919</v>
-      </c>
-      <c r="D72" t="s">
-        <v>41</v>
-      </c>
       <c r="F72" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H72" s="2">
-        <v>2.6932870370370371E-2</v>
+        <v>3.9953703703703707E-2</v>
       </c>
       <c r="I72" s="1">
-        <v>45845.421412037038</v>
+        <v>45628.821967592594</v>
       </c>
       <c r="J72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K72" t="s">
         <v>11</v>
@@ -2559,28 +2532,28 @@
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C73">
-        <v>2826</v>
+        <v>1842</v>
       </c>
       <c r="D73" t="s">
         <v>35</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H73" s="2">
-        <v>1.9675925925925924E-3</v>
+        <v>0</v>
       </c>
       <c r="I73" s="1">
-        <v>45845.421412037038</v>
+        <v>45628.821967592594</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K73" t="s">
         <v>11</v>
@@ -2588,25 +2561,25 @@
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C74">
-        <v>3666</v>
+        <v>1839</v>
       </c>
       <c r="D74" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H74" s="2">
-        <v>5.9606481481481481E-3</v>
+        <v>6.3541666666666668E-3</v>
       </c>
       <c r="I74" s="1">
-        <v>45845.421412037038</v>
+        <v>45628.821967592594</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -2617,28 +2590,28 @@
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C75">
-        <v>2828</v>
+        <v>1841</v>
       </c>
       <c r="D75" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H75" s="2">
-        <v>4.6064814814814814E-3</v>
+        <v>1.0810185185185185E-2</v>
       </c>
       <c r="I75" s="1">
-        <v>45845.421412037038</v>
+        <v>45663.459837962961</v>
       </c>
       <c r="J75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K75" t="s">
         <v>11</v>
@@ -2646,28 +2619,28 @@
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C76">
-        <v>2830</v>
+        <v>2270</v>
       </c>
       <c r="D76" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H76" s="2">
-        <v>0</v>
+        <v>5.324074074074074E-3</v>
       </c>
       <c r="I76" s="1">
-        <v>45845.422106481485</v>
+        <v>45663.460532407407</v>
       </c>
       <c r="J76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K76" t="s">
         <v>11</v>
@@ -2675,28 +2648,28 @@
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C77">
-        <v>2832</v>
+        <v>2714</v>
       </c>
       <c r="D77" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H77" s="2">
-        <v>0</v>
+        <v>8.067129629629629E-3</v>
       </c>
       <c r="I77" s="1">
-        <v>45845.422106481485</v>
+        <v>45663.461226851854</v>
       </c>
       <c r="J77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K77" t="s">
         <v>11</v>
@@ -2704,86 +2677,66 @@
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C78">
-        <v>2825</v>
+        <v>1843</v>
       </c>
       <c r="D78" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H78" s="2">
-        <v>0</v>
+        <v>3.1944444444444446E-3</v>
       </c>
       <c r="I78" s="1">
-        <v>45845.422800925924</v>
+        <v>45663.461226851854</v>
       </c>
       <c r="J78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K78" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B79" t="s">
-        <v>34</v>
-      </c>
-      <c r="C79">
-        <v>2827</v>
-      </c>
-      <c r="D79" t="s">
-        <v>43</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H79" s="2">
-        <v>6.4699074074074077E-3</v>
-      </c>
-      <c r="I79" s="1">
-        <v>45845.422800925924</v>
-      </c>
-      <c r="J79">
-        <v>0</v>
-      </c>
+      <c r="F79" s="2"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="1"/>
       <c r="K79" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
+        <v>30</v>
+      </c>
+      <c r="C80">
+        <v>1840</v>
+      </c>
+      <c r="D80" t="s">
         <v>34</v>
       </c>
-      <c r="C80">
-        <v>2919</v>
-      </c>
-      <c r="D80" t="s">
-        <v>41</v>
-      </c>
       <c r="F80" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H80" s="2">
-        <v>5.9027777777777776E-3</v>
+        <v>9.1435185185185178E-3</v>
       </c>
       <c r="I80" s="1">
-        <v>45873.462962962964</v>
+        <v>45663.461921296293</v>
       </c>
       <c r="J80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K80" t="s">
         <v>11</v>
@@ -2791,28 +2744,28 @@
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C81">
-        <v>2826</v>
+        <v>1842</v>
       </c>
       <c r="D81" t="s">
         <v>35</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H81" s="2">
-        <v>3.5532407407407409E-3</v>
+        <v>0</v>
       </c>
       <c r="I81" s="1">
-        <v>45873.462962962964</v>
+        <v>45663.461921296293</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K81" t="s">
         <v>11</v>
@@ -2820,25 +2773,25 @@
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C82">
-        <v>3666</v>
+        <v>1839</v>
       </c>
       <c r="D82" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H82" s="2">
-        <v>4.5949074074074078E-3</v>
+        <v>5.37037037037037E-3</v>
       </c>
       <c r="I82" s="1">
-        <v>45873.462962962964</v>
+        <v>45663.461921296293</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -2849,25 +2802,25 @@
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C83">
-        <v>2828</v>
+        <v>1841</v>
       </c>
       <c r="D83" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H83" s="2">
-        <v>5.4050925925925924E-3</v>
+        <v>0.50710648148148152</v>
       </c>
       <c r="I83" s="1">
-        <v>45873.462962962964</v>
+        <v>45691.627546296295</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -2878,28 +2831,28 @@
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C84">
-        <v>2830</v>
+        <v>2270</v>
       </c>
       <c r="D84" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H84" s="2">
-        <v>4.8495370370370368E-3</v>
+        <v>6.1574074074074074E-3</v>
       </c>
       <c r="I84" s="1">
-        <v>45873.46365740741</v>
+        <v>45691.628240740742</v>
       </c>
       <c r="J84">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K84" t="s">
         <v>11</v>
@@ -2907,28 +2860,28 @@
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C85">
-        <v>2829</v>
+        <v>2714</v>
       </c>
       <c r="D85" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H85" s="2">
-        <v>4.7337962962962967E-3</v>
+        <v>0</v>
       </c>
       <c r="I85" s="1">
-        <v>45873.46365740741</v>
+        <v>45691.628240740742</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K85" t="s">
         <v>11</v>
@@ -2936,86 +2889,66 @@
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C86">
-        <v>2832</v>
+        <v>1843</v>
       </c>
       <c r="D86" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H86" s="2">
-        <v>0</v>
+        <v>4.3981481481481484E-3</v>
       </c>
       <c r="I86" s="1">
-        <v>45873.46365740741</v>
+        <v>45691.628935185188</v>
       </c>
       <c r="J86">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K86" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B87" t="s">
-        <v>34</v>
-      </c>
-      <c r="C87">
-        <v>2825</v>
-      </c>
-      <c r="D87" t="s">
-        <v>40</v>
-      </c>
-      <c r="F87" s="2" t="s">
+      <c r="F87" s="2"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="1"/>
+      <c r="K87" t="s">
         <v>25</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H87" s="2">
-        <v>3.6805555555555554E-3</v>
-      </c>
-      <c r="I87" s="1">
-        <v>45873.46435185185</v>
-      </c>
-      <c r="J87">
-        <v>2</v>
-      </c>
-      <c r="K87" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
+        <v>30</v>
+      </c>
+      <c r="C88">
+        <v>1840</v>
+      </c>
+      <c r="D88" t="s">
         <v>34</v>
       </c>
-      <c r="C88">
-        <v>2827</v>
-      </c>
-      <c r="D88" t="s">
-        <v>43</v>
-      </c>
       <c r="F88" s="2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H88" s="2">
-        <v>2.210648148148148E-2</v>
+        <v>0.62365740740740738</v>
       </c>
       <c r="I88" s="1">
-        <v>45873.46435185185</v>
+        <v>45691.628935185188</v>
       </c>
       <c r="J88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K88" t="s">
         <v>11</v>
@@ -3023,28 +2956,28 @@
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C89">
-        <v>2919</v>
+        <v>1842</v>
       </c>
       <c r="D89" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H89" s="2">
-        <v>5.6944444444444447E-3</v>
+        <v>0</v>
       </c>
       <c r="I89" s="1">
-        <v>45901.920023148145</v>
+        <v>45691.629629629628</v>
       </c>
       <c r="J89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K89" t="s">
         <v>11</v>
@@ -3052,25 +2985,25 @@
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C90">
-        <v>2826</v>
+        <v>1839</v>
       </c>
       <c r="D90" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H90" s="2">
-        <v>3.6226851851851854E-3</v>
+        <v>5.0694444444444441E-3</v>
       </c>
       <c r="I90" s="1">
-        <v>45901.920023148145</v>
+        <v>45691.629629629628</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -3081,28 +3014,28 @@
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C91">
-        <v>3666</v>
+        <v>1841</v>
       </c>
       <c r="D91" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H91" s="2">
-        <v>5.8796296296296296E-3</v>
+        <v>1.2916666666666667E-2</v>
       </c>
       <c r="I91" s="1">
-        <v>45901.920717592591</v>
+        <v>45719.627314814818</v>
       </c>
       <c r="J91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K91" t="s">
         <v>11</v>
@@ -3110,28 +3043,28 @@
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C92">
-        <v>2828</v>
+        <v>2270</v>
       </c>
       <c r="D92" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H92" s="2">
-        <v>3.7152777777777778E-3</v>
+        <v>1.4085648148148147E-2</v>
       </c>
       <c r="I92" s="1">
-        <v>45901.920717592591</v>
+        <v>45719.627314814818</v>
       </c>
       <c r="J92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" t="s">
         <v>11</v>
@@ -3139,28 +3072,28 @@
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C93">
-        <v>2830</v>
+        <v>1843</v>
       </c>
       <c r="D93" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H93" s="2">
-        <v>0</v>
+        <v>7.5925925925925926E-3</v>
       </c>
       <c r="I93" s="1">
-        <v>45901.921412037038</v>
+        <v>45719.628009259257</v>
       </c>
       <c r="J93">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K93" t="s">
         <v>11</v>
@@ -3168,25 +3101,25 @@
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
+        <v>30</v>
+      </c>
+      <c r="C94">
+        <v>1840</v>
+      </c>
+      <c r="D94" t="s">
         <v>34</v>
       </c>
-      <c r="C94">
-        <v>2829</v>
-      </c>
-      <c r="D94" t="s">
-        <v>38</v>
-      </c>
       <c r="F94" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H94" s="2">
-        <v>4.8032407407407407E-3</v>
+        <v>1.3518518518518518E-2</v>
       </c>
       <c r="I94" s="1">
-        <v>45901.921412037038</v>
+        <v>45719.628009259257</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -3197,16 +3130,16 @@
     </row>
     <row r="95" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C95">
-        <v>2832</v>
+        <v>1842</v>
       </c>
       <c r="D95" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>13</v>
@@ -3215,10 +3148,10 @@
         <v>0</v>
       </c>
       <c r="I95" s="1">
-        <v>45901.921412037038</v>
+        <v>45719.628703703704</v>
       </c>
       <c r="J95">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K95" t="s">
         <v>11</v>
@@ -3226,25 +3159,25 @@
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C96">
-        <v>2825</v>
+        <v>1839</v>
       </c>
       <c r="D96" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H96" s="2">
-        <v>4.2245370370370371E-3</v>
+        <v>7.3726851851851852E-3</v>
       </c>
       <c r="I96" s="1">
-        <v>45901.922106481485</v>
+        <v>45719.628703703704</v>
       </c>
       <c r="J96">
         <v>1</v>
@@ -3255,28 +3188,28 @@
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C97">
-        <v>2827</v>
+        <v>1841</v>
       </c>
       <c r="D97" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H97" s="2">
-        <v>6.4814814814814813E-3</v>
+        <v>1.2638888888888889E-2</v>
       </c>
       <c r="I97" s="1">
-        <v>45901.922106481485</v>
+        <v>45754.710879629631</v>
       </c>
       <c r="J97">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K97" t="s">
         <v>11</v>
@@ -3284,28 +3217,28 @@
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C98">
-        <v>2919</v>
+        <v>2270</v>
       </c>
       <c r="D98" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H98" s="2">
-        <v>8.0787037037037043E-3</v>
+        <v>8.819444444444444E-3</v>
       </c>
       <c r="I98" s="1">
-        <v>45936.588773148149</v>
+        <v>45754.711574074077</v>
       </c>
       <c r="J98">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K98" t="s">
         <v>11</v>
@@ -3313,25 +3246,25 @@
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C99">
-        <v>2826</v>
+        <v>1843</v>
       </c>
       <c r="D99" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H99" s="2">
-        <v>9.5601851851851855E-3</v>
+        <v>1.3148148148148148E-2</v>
       </c>
       <c r="I99" s="1">
-        <v>45936.589467592596</v>
+        <v>45754.712268518517</v>
       </c>
       <c r="J99">
         <v>1</v>
@@ -3342,28 +3275,28 @@
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
+        <v>30</v>
+      </c>
+      <c r="C100">
+        <v>1840</v>
+      </c>
+      <c r="D100" t="s">
         <v>34</v>
       </c>
-      <c r="C100">
-        <v>3666</v>
-      </c>
-      <c r="D100" t="s">
-        <v>44</v>
-      </c>
       <c r="F100" s="2" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H100" s="2">
-        <v>0.15841435185185185</v>
+        <v>0.38033564814814813</v>
       </c>
       <c r="I100" s="1">
-        <v>45936.589467592596</v>
+        <v>45754.712962962964</v>
       </c>
       <c r="J100">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K100" t="s">
         <v>11</v>
@@ -3371,66 +3304,86 @@
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C101">
-        <v>2828</v>
+        <v>1842</v>
       </c>
       <c r="D101" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H101" s="2">
-        <v>4.1666666666666669E-4</v>
+        <v>0</v>
       </c>
       <c r="I101" s="1">
-        <v>45936.590162037035</v>
+        <v>45754.712962962964</v>
       </c>
       <c r="J101">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K101" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F102" s="2"/>
-      <c r="G102" s="1"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="1"/>
+      <c r="B102" t="s">
+        <v>30</v>
+      </c>
+      <c r="C102">
+        <v>1839</v>
+      </c>
+      <c r="D102" t="s">
+        <v>36</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H102" s="2">
+        <v>4.5428240740740741E-2</v>
+      </c>
+      <c r="I102" s="1">
+        <v>45754.71365740741</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
       <c r="K102" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C103">
-        <v>2830</v>
+        <v>1841</v>
       </c>
       <c r="D103" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H103" s="2">
-        <v>1.0358796296296297E-2</v>
+        <v>1.1759259259259259E-2</v>
       </c>
       <c r="I103" s="1">
-        <v>45936.590162037035</v>
+        <v>45782.626851851855</v>
       </c>
       <c r="J103">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K103" t="s">
         <v>11</v>
@@ -3438,28 +3391,28 @@
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C104">
-        <v>2832</v>
+        <v>2270</v>
       </c>
       <c r="D104" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H104" s="2">
-        <v>0</v>
+        <v>1.1134259259259259E-2</v>
       </c>
       <c r="I104" s="1">
-        <v>45936.590856481482</v>
+        <v>45782.626851851855</v>
       </c>
       <c r="J104">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K104" t="s">
         <v>11</v>
@@ -3467,25 +3420,25 @@
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C105">
-        <v>2825</v>
+        <v>1843</v>
       </c>
       <c r="D105" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H105" s="2">
-        <v>5.1273148148148146E-3</v>
+        <v>1.7048611111111112E-2</v>
       </c>
       <c r="I105" s="1">
-        <v>45936.591550925928</v>
+        <v>45782.627546296295</v>
       </c>
       <c r="J105">
         <v>2</v>
@@ -3496,28 +3449,28 @@
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106">
+        <v>1840</v>
+      </c>
+      <c r="D106" t="s">
         <v>34</v>
       </c>
-      <c r="C106">
-        <v>2827</v>
-      </c>
-      <c r="D106" t="s">
-        <v>43</v>
-      </c>
       <c r="F106" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H106" s="2">
-        <v>7.7546296296296295E-3</v>
+        <v>1.2662037037037038E-2</v>
       </c>
       <c r="I106" s="1">
-        <v>45936.591550925928</v>
+        <v>45782.628240740742</v>
       </c>
       <c r="J106">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K106" t="s">
         <v>11</v>
@@ -3525,28 +3478,28 @@
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C107">
-        <v>4883</v>
+        <v>1842</v>
       </c>
       <c r="D107" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H107" s="2">
-        <v>7.4768518518518517E-3</v>
+        <v>0</v>
       </c>
       <c r="I107" s="1">
-        <v>45964.669328703705</v>
+        <v>45782.628935185188</v>
       </c>
       <c r="J107">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K107" t="s">
         <v>11</v>
@@ -3554,95 +3507,95 @@
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C108">
-        <v>4884</v>
+        <v>1839</v>
       </c>
       <c r="D108" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H108" s="2">
-        <v>1.1655092592592592E-2</v>
+        <v>4.1678240740740738E-2</v>
       </c>
       <c r="I108" s="1">
-        <v>45964.670023148145</v>
+        <v>45782.628935185188</v>
       </c>
       <c r="J108">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K108" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B109" t="s">
-        <v>34</v>
-      </c>
-      <c r="C109">
-        <v>2919</v>
-      </c>
-      <c r="D109" t="s">
-        <v>41</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H109" s="2">
-        <v>8.564814814814815E-3</v>
-      </c>
-      <c r="I109" s="1">
-        <v>45964.670023148145</v>
-      </c>
-      <c r="J109">
-        <v>2</v>
-      </c>
+      <c r="F109" s="2"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="2"/>
+      <c r="I109" s="1"/>
       <c r="K109" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B110" t="s">
+        <v>30</v>
+      </c>
+      <c r="C110">
+        <v>1841</v>
+      </c>
+      <c r="D110" t="s">
+        <v>31</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H110" s="2">
+        <v>1.2800925925925926E-2</v>
+      </c>
+      <c r="I110" s="1">
+        <v>45810.668171296296</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F110" s="2"/>
-      <c r="G110" s="1"/>
-      <c r="H110" s="2"/>
-      <c r="I110" s="1"/>
-      <c r="K110" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="111" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C111">
-        <v>2826</v>
+        <v>2270</v>
       </c>
       <c r="D111" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="G111" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H111" s="2">
-        <v>7.5925925925925926E-3</v>
+        <v>4.9074074074074072E-3</v>
       </c>
       <c r="I111" s="1">
-        <v>45964.670717592591</v>
+        <v>45810.668865740743</v>
       </c>
       <c r="J111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K111" t="s">
         <v>11</v>
@@ -3650,28 +3603,28 @@
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C112">
-        <v>3666</v>
+        <v>1843</v>
       </c>
       <c r="D112" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H112" s="2">
-        <v>3.259259259259259E-2</v>
+        <v>6.3541666666666668E-3</v>
       </c>
       <c r="I112" s="1">
-        <v>45964.670717592591</v>
+        <v>45810.669560185182</v>
       </c>
       <c r="J112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112" t="s">
         <v>11</v>
@@ -3679,25 +3632,25 @@
     </row>
     <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
+        <v>30</v>
+      </c>
+      <c r="C113">
+        <v>1840</v>
+      </c>
+      <c r="D113" t="s">
         <v>34</v>
       </c>
-      <c r="C113">
-        <v>2828</v>
-      </c>
-      <c r="D113" t="s">
-        <v>36</v>
-      </c>
       <c r="F113" s="2" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H113" s="2">
-        <v>7.7777777777777776E-3</v>
+        <v>5.092592592592593E-3</v>
       </c>
       <c r="I113" s="1">
-        <v>45964.671412037038</v>
+        <v>45810.669560185182</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -3708,25 +3661,25 @@
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C114">
-        <v>2830</v>
+        <v>1842</v>
       </c>
       <c r="D114" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H114" s="2">
-        <v>8.6574074074074071E-3</v>
+        <v>0</v>
       </c>
       <c r="I114" s="1">
-        <v>45964.672106481485</v>
+        <v>45810.670254629629</v>
       </c>
       <c r="J114">
         <v>3</v>
@@ -3737,28 +3690,28 @@
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C115">
-        <v>2832</v>
+        <v>1839</v>
       </c>
       <c r="D115" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H115" s="2">
-        <v>0</v>
+        <v>4.3981481481481484E-3</v>
       </c>
       <c r="I115" s="1">
-        <v>45964.672800925924</v>
+        <v>45810.670949074076</v>
       </c>
       <c r="J115">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K115" t="s">
         <v>11</v>
@@ -3766,28 +3719,28 @@
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C116">
-        <v>2825</v>
+        <v>1841</v>
       </c>
       <c r="D116" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H116" s="2">
+        <v>1.6261574074074074E-2</v>
+      </c>
+      <c r="I116" s="1">
+        <v>45845.419328703705</v>
+      </c>
+      <c r="J116">
         <v>0</v>
-      </c>
-      <c r="I116" s="1">
-        <v>45964.672800925924</v>
-      </c>
-      <c r="J116">
-        <v>5</v>
       </c>
       <c r="K116" t="s">
         <v>11</v>
@@ -3795,25 +3748,25 @@
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C117">
-        <v>2827</v>
+        <v>2270</v>
       </c>
       <c r="D117" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H117" s="2">
-        <v>7.8009259259259256E-3</v>
+        <v>1.1527777777777777E-2</v>
       </c>
       <c r="I117" s="1">
-        <v>45964.673495370371</v>
+        <v>45845.419328703705</v>
       </c>
       <c r="J117">
         <v>1</v>
@@ -3824,25 +3777,25 @@
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C118">
-        <v>4883</v>
+        <v>1843</v>
       </c>
       <c r="D118" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H118" s="2">
-        <v>5.0231481481481481E-3</v>
+        <v>1.2094907407407407E-2</v>
       </c>
       <c r="I118" s="1">
-        <v>45992.504745370374</v>
+        <v>45845.420023148145</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -3853,28 +3806,28 @@
     </row>
     <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
+        <v>30</v>
+      </c>
+      <c r="C119">
+        <v>1840</v>
+      </c>
+      <c r="D119" t="s">
         <v>34</v>
       </c>
-      <c r="C119">
-        <v>4884</v>
-      </c>
-      <c r="D119" t="s">
-        <v>46</v>
-      </c>
       <c r="F119" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H119" s="2">
-        <v>6.076388888888889E-3</v>
+        <v>1.5104166666666667E-2</v>
       </c>
       <c r="I119" s="1">
-        <v>45992.505439814813</v>
+        <v>45845.420023148145</v>
       </c>
       <c r="J119">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K119" t="s">
         <v>11</v>
@@ -3882,25 +3835,25 @@
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C120">
-        <v>2919</v>
+        <v>1842</v>
       </c>
       <c r="D120" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H120" s="2">
-        <v>4.5486111111111109E-3</v>
+        <v>0</v>
       </c>
       <c r="I120" s="1">
-        <v>45992.505439814813</v>
+        <v>45845.420717592591</v>
       </c>
       <c r="J120">
         <v>2</v>
@@ -3911,28 +3864,28 @@
     </row>
     <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C121">
-        <v>2826</v>
+        <v>1839</v>
       </c>
       <c r="D121" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G121" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H121" s="2">
-        <v>5.7870370370370367E-3</v>
+        <v>1.0798611111111111E-2</v>
       </c>
       <c r="I121" s="1">
-        <v>45992.50613425926</v>
+        <v>45845.420717592591</v>
       </c>
       <c r="J121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K121" t="s">
         <v>11</v>
@@ -3940,25 +3893,25 @@
     </row>
     <row r="122" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C122">
-        <v>3666</v>
+        <v>1841</v>
       </c>
       <c r="D122" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H122" s="2">
-        <v>1.7893518518518517E-2</v>
+        <v>1.5208333333333334E-2</v>
       </c>
       <c r="I122" s="1">
-        <v>45992.50613425926</v>
+        <v>45873.460185185184</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -3969,25 +3922,25 @@
     </row>
     <row r="123" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C123">
-        <v>2828</v>
+        <v>2270</v>
       </c>
       <c r="D123" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H123" s="2">
-        <v>1.0648148148148149E-3</v>
+        <v>2.0833333333333335E-4</v>
       </c>
       <c r="I123" s="1">
-        <v>45992.50613425926</v>
+        <v>45873.460185185184</v>
       </c>
       <c r="J123">
         <v>3</v>
@@ -4002,30 +3955,30 @@
       <c r="H124" s="2"/>
       <c r="I124" s="1"/>
       <c r="K124" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C125">
-        <v>2830</v>
+        <v>3874</v>
       </c>
       <c r="D125" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H125" s="2">
-        <v>0</v>
+        <v>7.6851851851851855E-3</v>
       </c>
       <c r="I125" s="1">
-        <v>45992.506828703707</v>
+        <v>45873.460879629631</v>
       </c>
       <c r="J125">
         <v>3</v>
@@ -4036,28 +3989,28 @@
     </row>
     <row r="126" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C126">
-        <v>2832</v>
+        <v>1843</v>
       </c>
       <c r="D126" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H126" s="2">
+        <v>1.474537037037037E-2</v>
+      </c>
+      <c r="I126" s="1">
+        <v>45873.460879629631</v>
+      </c>
+      <c r="J126">
         <v>0</v>
-      </c>
-      <c r="I126" s="1">
-        <v>45992.506828703707</v>
-      </c>
-      <c r="J126">
-        <v>3</v>
       </c>
       <c r="K126" t="s">
         <v>11</v>
@@ -4065,28 +4018,28 @@
     </row>
     <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C127">
-        <v>2825</v>
+        <v>2008</v>
       </c>
       <c r="D127" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H127" s="2">
+        <v>7.9861111111111105E-3</v>
+      </c>
+      <c r="I127" s="1">
+        <v>45873.460879629631</v>
+      </c>
+      <c r="J127">
         <v>0</v>
-      </c>
-      <c r="I127" s="1">
-        <v>45992.506828703707</v>
-      </c>
-      <c r="J127">
-        <v>3</v>
       </c>
       <c r="K127" t="s">
         <v>11</v>
@@ -4094,28 +4047,28 @@
     </row>
     <row r="128" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
+        <v>30</v>
+      </c>
+      <c r="C128">
+        <v>1840</v>
+      </c>
+      <c r="D128" t="s">
         <v>34</v>
       </c>
-      <c r="C128">
-        <v>2827</v>
-      </c>
-      <c r="D128" t="s">
-        <v>43</v>
-      </c>
       <c r="F128" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H128" s="2">
-        <v>0</v>
+        <v>2.3287037037037037E-2</v>
       </c>
       <c r="I128" s="1">
-        <v>45992.506828703707</v>
+        <v>45873.461574074077</v>
       </c>
       <c r="J128">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K128" t="s">
         <v>11</v>
@@ -4123,25 +4076,25 @@
     </row>
     <row r="129" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C129">
-        <v>4883</v>
+        <v>2043</v>
       </c>
       <c r="D129" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H129" s="2">
-        <v>5.9837962962962961E-3</v>
+        <v>9.0856481481481483E-3</v>
       </c>
       <c r="I129" s="1">
-        <v>46027.673842592594</v>
+        <v>45873.461574074077</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -4152,28 +4105,28 @@
     </row>
     <row r="130" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C130">
-        <v>4884</v>
+        <v>3875</v>
       </c>
       <c r="D130" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H130" s="2">
-        <v>5.8680555555555552E-3</v>
+        <v>8.9120370370370378E-3</v>
       </c>
       <c r="I130" s="1">
-        <v>46027.674537037034</v>
+        <v>45873.462268518517</v>
       </c>
       <c r="J130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K130" t="s">
         <v>11</v>
@@ -4181,28 +4134,28 @@
     </row>
     <row r="131" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C131">
-        <v>2919</v>
+        <v>1839</v>
       </c>
       <c r="D131" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H131" s="2">
-        <v>1.074074074074074E-2</v>
+        <v>6.8055555555555551E-3</v>
       </c>
       <c r="I131" s="1">
-        <v>46027.674537037034</v>
+        <v>45873.462268518517</v>
       </c>
       <c r="J131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K131" t="s">
         <v>11</v>
@@ -4210,25 +4163,25 @@
     </row>
     <row r="132" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C132">
-        <v>2826</v>
+        <v>1841</v>
       </c>
       <c r="D132" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H132" s="2">
-        <v>5.6249999999999998E-3</v>
+        <v>7.8472222222222224E-3</v>
       </c>
       <c r="I132" s="1">
-        <v>46027.67523148148</v>
+        <v>45901.91851851852</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -4239,28 +4192,28 @@
     </row>
     <row r="133" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C133">
-        <v>3666</v>
+        <v>2270</v>
       </c>
       <c r="D133" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H133" s="2">
-        <v>0</v>
+        <v>5.208333333333333E-3</v>
       </c>
       <c r="I133" s="1">
-        <v>46027.675925925927</v>
+        <v>45901.91851851852</v>
       </c>
       <c r="J133">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K133" t="s">
         <v>11</v>
@@ -4268,28 +4221,28 @@
     </row>
     <row r="134" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C134">
-        <v>2828</v>
+        <v>3874</v>
       </c>
       <c r="D134" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H134" s="2">
-        <v>6.2037037037037035E-3</v>
+        <v>4.6874999999999998E-3</v>
       </c>
       <c r="I134" s="1">
-        <v>46027.675925925927</v>
+        <v>45901.919212962966</v>
       </c>
       <c r="J134">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K134" t="s">
         <v>11</v>
@@ -4297,28 +4250,28 @@
     </row>
     <row r="135" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C135">
-        <v>2830</v>
+        <v>1843</v>
       </c>
       <c r="D135" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H135" s="2">
+        <v>5.3819444444444444E-3</v>
+      </c>
+      <c r="I135" s="1">
+        <v>45901.919212962966</v>
+      </c>
+      <c r="J135">
         <v>0</v>
-      </c>
-      <c r="I135" s="1">
-        <v>46027.676620370374</v>
-      </c>
-      <c r="J135">
-        <v>5</v>
       </c>
       <c r="K135" t="s">
         <v>11</v>
@@ -4326,28 +4279,28 @@
     </row>
     <row r="136" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C136">
-        <v>2832</v>
+        <v>4745</v>
       </c>
       <c r="D136" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H136" s="2">
-        <v>0</v>
+        <v>4.7569444444444447E-3</v>
       </c>
       <c r="I136" s="1">
-        <v>46027.677314814813</v>
+        <v>45901.919907407406</v>
       </c>
       <c r="J136">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K136" t="s">
         <v>11</v>
@@ -4355,83 +4308,63 @@
     </row>
     <row r="137" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C137">
-        <v>2825</v>
+        <v>4736</v>
       </c>
       <c r="D137" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H137" s="2">
-        <v>0</v>
+        <v>1.5046296296296297E-4</v>
       </c>
       <c r="I137" s="1">
-        <v>46027.677314814813</v>
+        <v>45901.919907407406</v>
       </c>
       <c r="J137">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K137" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="138" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B138" t="s">
-        <v>34</v>
-      </c>
-      <c r="C138">
-        <v>2827</v>
-      </c>
-      <c r="D138" t="s">
-        <v>43</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H138" s="2">
-        <v>7.743055555555556E-3</v>
-      </c>
-      <c r="I138" s="1">
-        <v>46027.67800925926</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
+      <c r="F138" s="2"/>
+      <c r="G138" s="1"/>
+      <c r="H138" s="2"/>
+      <c r="I138" s="1"/>
       <c r="K138" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="139" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C139">
-        <v>4883</v>
+        <v>2008</v>
       </c>
       <c r="D139" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H139" s="2">
-        <v>6.7939814814814816E-3</v>
+        <v>4.9305555555555552E-3</v>
       </c>
       <c r="I139" s="1">
-        <v>46055.713425925926</v>
+        <v>45901.920601851853</v>
       </c>
       <c r="J139">
         <v>0</v>
@@ -4442,28 +4375,28 @@
     </row>
     <row r="140" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
+        <v>30</v>
+      </c>
+      <c r="C140">
+        <v>1840</v>
+      </c>
+      <c r="D140" t="s">
         <v>34</v>
       </c>
-      <c r="C140">
-        <v>4884</v>
-      </c>
-      <c r="D140" t="s">
-        <v>46</v>
-      </c>
       <c r="F140" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H140" s="2">
-        <v>6.9328703703703705E-3</v>
+        <v>0.29428240740740741</v>
       </c>
       <c r="I140" s="1">
-        <v>46055.714120370372</v>
+        <v>45901.920601851853</v>
       </c>
       <c r="J140">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K140" t="s">
         <v>11</v>
@@ -4471,28 +4404,28 @@
     </row>
     <row r="141" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C141">
-        <v>2919</v>
+        <v>2043</v>
       </c>
       <c r="D141" t="s">
         <v>41</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H141" s="2">
-        <v>6.7245370370370367E-3</v>
+        <v>4.2245370370370371E-3</v>
       </c>
       <c r="I141" s="1">
-        <v>46055.714814814812</v>
+        <v>45901.920601851853</v>
       </c>
       <c r="J141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K141" t="s">
         <v>11</v>
@@ -4500,25 +4433,25 @@
     </row>
     <row r="142" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C142">
-        <v>2826</v>
+        <v>1839</v>
       </c>
       <c r="D142" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H142" s="2">
-        <v>9.5138888888888894E-3</v>
+        <v>3.9814814814814817E-3</v>
       </c>
       <c r="I142" s="1">
-        <v>46055.714814814812</v>
+        <v>45901.921296296299</v>
       </c>
       <c r="J142">
         <v>0</v>
@@ -4529,25 +4462,25 @@
     </row>
     <row r="143" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C143">
-        <v>3666</v>
+        <v>1841</v>
       </c>
       <c r="D143" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H143" s="2">
-        <v>7.2569444444444443E-3</v>
+        <v>1.3923611111111111E-2</v>
       </c>
       <c r="I143" s="1">
-        <v>46055.715509259258</v>
+        <v>45936.585300925923</v>
       </c>
       <c r="J143">
         <v>1</v>
@@ -4558,28 +4491,28 @@
     </row>
     <row r="144" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C144">
-        <v>2828</v>
+        <v>2270</v>
       </c>
       <c r="D144" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H144" s="2">
-        <v>6.5162037037037037E-3</v>
+        <v>0</v>
       </c>
       <c r="I144" s="1">
-        <v>46055.716203703705</v>
+        <v>45936.585300925923</v>
       </c>
       <c r="J144">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K144" t="s">
         <v>11</v>
@@ -4587,28 +4520,28 @@
     </row>
     <row r="145" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C145">
-        <v>2830</v>
+        <v>3874</v>
       </c>
       <c r="D145" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H145" s="2">
-        <v>9.0162037037037034E-3</v>
+        <v>0</v>
       </c>
       <c r="I145" s="1">
-        <v>46055.716898148145</v>
+        <v>45936.585995370369</v>
       </c>
       <c r="J145">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K145" t="s">
         <v>11</v>
@@ -4616,28 +4549,28 @@
     </row>
     <row r="146" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C146">
-        <v>2832</v>
+        <v>1843</v>
       </c>
       <c r="D146" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H146" s="2">
+        <v>9.2361111111111116E-3</v>
+      </c>
+      <c r="I146" s="1">
+        <v>45936.585995370369</v>
+      </c>
+      <c r="J146">
         <v>0</v>
-      </c>
-      <c r="I146" s="1">
-        <v>46055.717592592591</v>
-      </c>
-      <c r="J146">
-        <v>5</v>
       </c>
       <c r="K146" t="s">
         <v>11</v>
@@ -4645,28 +4578,28 @@
     </row>
     <row r="147" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C147">
-        <v>2825</v>
+        <v>4745</v>
       </c>
       <c r="D147" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H147" s="2">
-        <v>6.9097222222222225E-3</v>
+        <v>9.4444444444444445E-3</v>
       </c>
       <c r="I147" s="1">
-        <v>46055.717592592591</v>
+        <v>45936.586689814816</v>
       </c>
       <c r="J147">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K147" t="s">
         <v>11</v>
@@ -4674,28 +4607,28 @@
     </row>
     <row r="148" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C148">
-        <v>2827</v>
+        <v>4736</v>
       </c>
       <c r="D148" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H148" s="2">
-        <v>6.7824074074074071E-3</v>
+        <v>0</v>
       </c>
       <c r="I148" s="1">
-        <v>46055.718287037038</v>
+        <v>45936.586689814816</v>
       </c>
       <c r="J148">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K148" t="s">
         <v>11</v>
@@ -4703,25 +4636,25 @@
     </row>
     <row r="149" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C149">
-        <v>4883</v>
+        <v>2008</v>
       </c>
       <c r="D149" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H149" s="2">
-        <v>6.0648148148148145E-3</v>
+        <v>9.0393518518518522E-3</v>
       </c>
       <c r="I149" s="1">
-        <v>46083.671643518515</v>
+        <v>45936.587384259263</v>
       </c>
       <c r="J149">
         <v>0</v>
@@ -4732,28 +4665,28 @@
     </row>
     <row r="150" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
+        <v>30</v>
+      </c>
+      <c r="C150">
+        <v>1840</v>
+      </c>
+      <c r="D150" t="s">
         <v>34</v>
       </c>
-      <c r="C150">
-        <v>2919</v>
-      </c>
-      <c r="D150" t="s">
-        <v>41</v>
-      </c>
       <c r="F150" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G150" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H150" s="2">
-        <v>9.7569444444444448E-3</v>
+        <v>1.238425925925926E-2</v>
       </c>
       <c r="I150" s="1">
-        <v>46083.671643518515</v>
+        <v>45936.588078703702</v>
       </c>
       <c r="J150">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K150" t="s">
         <v>11</v>
@@ -4761,28 +4694,28 @@
     </row>
     <row r="151" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C151">
-        <v>2826</v>
+        <v>2043</v>
       </c>
       <c r="D151" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H151" s="2">
-        <v>4.2476851851851851E-3</v>
+        <v>0</v>
       </c>
       <c r="I151" s="1">
-        <v>46083.672337962962</v>
+        <v>45936.588078703702</v>
       </c>
       <c r="J151">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K151" t="s">
         <v>11</v>
@@ -4790,28 +4723,28 @@
     </row>
     <row r="152" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C152">
-        <v>3666</v>
+        <v>1839</v>
       </c>
       <c r="D152" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H152" s="2">
-        <v>5.8333333333333336E-3</v>
+        <v>8.8310185185185193E-3</v>
       </c>
       <c r="I152" s="1">
-        <v>46083.672337962962</v>
+        <v>45936.588773148149</v>
       </c>
       <c r="J152">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K152" t="s">
         <v>11</v>
@@ -4819,28 +4752,28 @@
     </row>
     <row r="153" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C153">
-        <v>2828</v>
+        <v>1841</v>
       </c>
       <c r="D153" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G153" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H153" s="2">
-        <v>4.5717592592592589E-3</v>
+        <v>1.2789351851851852E-2</v>
       </c>
       <c r="I153" s="1">
-        <v>46083.673032407409</v>
+        <v>45964.669212962966</v>
       </c>
       <c r="J153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K153" t="s">
         <v>11</v>
@@ -4848,28 +4781,28 @@
     </row>
     <row r="154" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C154">
-        <v>2830</v>
+        <v>2270</v>
       </c>
       <c r="D154" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H154" s="2">
-        <v>5.5092592592592589E-3</v>
+        <v>8.3796296296296292E-3</v>
       </c>
       <c r="I154" s="1">
-        <v>46083.673726851855</v>
+        <v>45964.669907407406</v>
       </c>
       <c r="J154">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K154" t="s">
         <v>11</v>
@@ -4877,25 +4810,25 @@
     </row>
     <row r="155" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C155">
-        <v>2832</v>
+        <v>3874</v>
       </c>
       <c r="D155" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H155" s="2">
-        <v>5.2199074074074075E-3</v>
+        <v>0</v>
       </c>
       <c r="I155" s="1">
-        <v>46083.673726851855</v>
+        <v>45964.670601851853</v>
       </c>
       <c r="J155">
         <v>4</v>
@@ -4905,58 +4838,38 @@
       </c>
     </row>
     <row r="156" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B156" t="s">
-        <v>34</v>
-      </c>
-      <c r="C156">
-        <v>2825</v>
-      </c>
-      <c r="D156" t="s">
-        <v>40</v>
-      </c>
-      <c r="F156" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H156" s="2">
-        <v>4.4444444444444444E-3</v>
-      </c>
-      <c r="I156" s="1">
-        <v>46083.674421296295</v>
-      </c>
-      <c r="J156">
-        <v>4</v>
-      </c>
+      <c r="F156" s="2"/>
+      <c r="G156" s="1"/>
+      <c r="H156" s="2"/>
+      <c r="I156" s="1"/>
       <c r="K156" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="157" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C157">
-        <v>2827</v>
+        <v>1843</v>
       </c>
       <c r="D157" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H157" s="2">
+        <v>8.472222222222223E-3</v>
+      </c>
+      <c r="I157" s="1">
+        <v>45964.670601851853</v>
+      </c>
+      <c r="J157">
         <v>0</v>
-      </c>
-      <c r="I157" s="1">
-        <v>46083.675115740742</v>
-      </c>
-      <c r="J157">
-        <v>4</v>
       </c>
       <c r="K157" t="s">
         <v>11</v>
@@ -4964,28 +4877,28 @@
     </row>
     <row r="158" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C158">
-        <v>2919</v>
+        <v>4745</v>
       </c>
       <c r="D158" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H158" s="2">
-        <v>1.3888888888888888E-2</v>
+        <v>8.2291666666666659E-3</v>
       </c>
       <c r="I158" s="1">
-        <v>46118.683217592596</v>
+        <v>45964.671296296299</v>
       </c>
       <c r="J158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K158" t="s">
         <v>11</v>
@@ -4993,28 +4906,28 @@
     </row>
     <row r="159" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C159">
-        <v>2826</v>
+        <v>4736</v>
       </c>
       <c r="D159" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H159" s="2">
-        <v>2.8935185185185184E-3</v>
+        <v>0</v>
       </c>
       <c r="I159" s="1">
-        <v>46118.683217592596</v>
+        <v>45964.671296296299</v>
       </c>
       <c r="J159">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K159" t="s">
         <v>11</v>
@@ -5022,25 +4935,25 @@
     </row>
     <row r="160" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C160">
-        <v>3666</v>
+        <v>2008</v>
       </c>
       <c r="D160" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H160" s="2">
-        <v>7.1875000000000003E-3</v>
+        <v>1.3159722222222222E-2</v>
       </c>
       <c r="I160" s="1">
-        <v>46118.683912037035</v>
+        <v>45964.671990740739</v>
       </c>
       <c r="J160">
         <v>0</v>
@@ -5051,28 +4964,28 @@
     </row>
     <row r="161" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
+        <v>30</v>
+      </c>
+      <c r="C161">
+        <v>1840</v>
+      </c>
+      <c r="D161" t="s">
         <v>34</v>
       </c>
-      <c r="C161">
-        <v>2828</v>
-      </c>
-      <c r="D161" t="s">
-        <v>36</v>
-      </c>
       <c r="F161" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H161" s="2">
-        <v>1.4155092592592592E-2</v>
+        <v>0</v>
       </c>
       <c r="I161" s="1">
-        <v>46118.683912037035</v>
+        <v>45964.671990740739</v>
       </c>
       <c r="J161">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K161" t="s">
         <v>11</v>
@@ -5080,28 +4993,28 @@
     </row>
     <row r="162" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B162" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C162">
-        <v>4883</v>
+        <v>2043</v>
       </c>
       <c r="D162" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H162" s="2">
-        <v>7.5115740740740742E-3</v>
+        <v>0</v>
       </c>
       <c r="I162" s="1">
-        <v>46118.684606481482</v>
+        <v>45964.672685185185</v>
       </c>
       <c r="J162">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K162" t="s">
         <v>11</v>
@@ -5109,92 +5022,92 @@
     </row>
     <row r="163" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C163">
-        <v>2830</v>
+        <v>1839</v>
       </c>
       <c r="D163" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H163" s="2">
-        <v>8.1018518518518514E-3</v>
+        <v>1.8518518518518518E-4</v>
       </c>
       <c r="I163" s="1">
-        <v>46118.685300925928</v>
+        <v>45964.673379629632</v>
       </c>
       <c r="J163">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K163" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="164" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B164" t="s">
-        <v>34</v>
-      </c>
-      <c r="C164">
-        <v>2832</v>
-      </c>
-      <c r="D164" t="s">
-        <v>39</v>
-      </c>
-      <c r="F164" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G164" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H164" s="2">
-        <v>2.9513888888888888E-3</v>
-      </c>
-      <c r="I164" s="1">
-        <v>46118.685300925928</v>
-      </c>
-      <c r="J164">
-        <v>1</v>
-      </c>
+      <c r="F164" s="2"/>
+      <c r="G164" s="1"/>
+      <c r="H164" s="2"/>
+      <c r="I164" s="1"/>
       <c r="K164" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B165" t="s">
+        <v>30</v>
+      </c>
+      <c r="C165">
+        <v>1841</v>
+      </c>
+      <c r="D165" t="s">
+        <v>31</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H165" s="2">
+        <v>1.2812499999999999E-2</v>
+      </c>
+      <c r="I165" s="1">
+        <v>45992.501967592594</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F165" s="2"/>
-      <c r="G165" s="1"/>
-      <c r="H165" s="2"/>
-      <c r="I165" s="1"/>
-      <c r="K165" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="166" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B166" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C166">
-        <v>2825</v>
+        <v>2270</v>
       </c>
       <c r="D166" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H166" s="2">
-        <v>7.6388888888888886E-3</v>
+        <v>0</v>
       </c>
       <c r="I166" s="1">
-        <v>46118.685995370368</v>
+        <v>45992.502662037034</v>
       </c>
       <c r="J166">
         <v>3</v>
@@ -5205,66 +5118,86 @@
     </row>
     <row r="167" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C167">
-        <v>2827</v>
+        <v>3874</v>
       </c>
       <c r="D167" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H167" s="2">
-        <v>4.9768518518518521E-3</v>
+        <v>0</v>
       </c>
       <c r="I167" s="1">
-        <v>46118.686689814815</v>
+        <v>45992.502662037034</v>
       </c>
       <c r="J167">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K167" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="168" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F168" s="2"/>
-      <c r="G168" s="1"/>
-      <c r="H168" s="2"/>
-      <c r="I168" s="1"/>
+      <c r="B168" t="s">
+        <v>30</v>
+      </c>
+      <c r="C168">
+        <v>1843</v>
+      </c>
+      <c r="D168" t="s">
+        <v>33</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H168" s="2">
+        <v>8.9814814814814809E-3</v>
+      </c>
+      <c r="I168" s="1">
+        <v>45992.50335648148</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
       <c r="K168" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="169" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B169" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C169">
-        <v>2919</v>
+        <v>4745</v>
       </c>
       <c r="D169" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H169" s="2">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="I169" s="1">
+        <v>45992.50335648148</v>
+      </c>
+      <c r="J169">
         <v>0</v>
-      </c>
-      <c r="I169" s="1">
-        <v>46146.58761574074</v>
-      </c>
-      <c r="J169">
-        <v>4</v>
       </c>
       <c r="K169" t="s">
         <v>11</v>
@@ -5272,28 +5205,28 @@
     </row>
     <row r="170" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B170" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C170">
-        <v>2826</v>
+        <v>4736</v>
       </c>
       <c r="D170" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H170" s="2">
-        <v>3.2175925925925926E-3</v>
+        <v>0</v>
       </c>
       <c r="I170" s="1">
-        <v>46146.588310185187</v>
+        <v>45992.504050925927</v>
       </c>
       <c r="J170">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K170" t="s">
         <v>11</v>
@@ -5301,28 +5234,28 @@
     </row>
     <row r="171" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B171" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C171">
-        <v>3666</v>
+        <v>2008</v>
       </c>
       <c r="D171" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H171" s="2">
-        <v>6.9560185185185185E-3</v>
+        <v>0</v>
       </c>
       <c r="I171" s="1">
-        <v>46146.588310185187</v>
+        <v>45992.504050925927</v>
       </c>
       <c r="J171">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K171" t="s">
         <v>11</v>
@@ -5330,86 +5263,66 @@
     </row>
     <row r="172" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B172" t="s">
+        <v>30</v>
+      </c>
+      <c r="C172">
+        <v>1840</v>
+      </c>
+      <c r="D172" t="s">
         <v>34</v>
       </c>
-      <c r="C172">
-        <v>2828</v>
-      </c>
-      <c r="D172" t="s">
-        <v>36</v>
-      </c>
       <c r="F172" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H172" s="2">
-        <v>4.9537037037037041E-3</v>
+        <v>8.5995370370370375E-3</v>
       </c>
       <c r="I172" s="1">
-        <v>46146.589004629626</v>
+        <v>45992.504050925927</v>
       </c>
       <c r="J172">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K172" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="173" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B173" t="s">
-        <v>34</v>
-      </c>
-      <c r="C173">
-        <v>4883</v>
-      </c>
-      <c r="D173" t="s">
-        <v>45</v>
-      </c>
-      <c r="F173" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G173" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H173" s="2">
-        <v>4.2245370370370371E-3</v>
-      </c>
-      <c r="I173" s="1">
-        <v>46146.589699074073</v>
-      </c>
-      <c r="J173">
-        <v>0</v>
-      </c>
+      <c r="F173" s="2"/>
+      <c r="G173" s="1"/>
+      <c r="H173" s="2"/>
+      <c r="I173" s="1"/>
       <c r="K173" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C174">
-        <v>2830</v>
+        <v>2043</v>
       </c>
       <c r="D174" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H174" s="2">
-        <v>6.5162037037037037E-3</v>
+        <v>0</v>
       </c>
       <c r="I174" s="1">
-        <v>46146.589699074073</v>
+        <v>45992.504745370374</v>
       </c>
       <c r="J174">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K174" t="s">
         <v>11</v>
@@ -5417,28 +5330,28 @@
     </row>
     <row r="175" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B175" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C175">
-        <v>2832</v>
+        <v>1839</v>
       </c>
       <c r="D175" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H175" s="2">
-        <v>4.7685185185185183E-3</v>
+        <v>5.6134259259259262E-3</v>
       </c>
       <c r="I175" s="1">
-        <v>46146.59039351852</v>
+        <v>45992.504745370374</v>
       </c>
       <c r="J175">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K175" t="s">
         <v>11</v>
@@ -5446,28 +5359,28 @@
     </row>
     <row r="176" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B176" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C176">
-        <v>2825</v>
+        <v>1841</v>
       </c>
       <c r="D176" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H176" s="2">
-        <v>4.0625000000000001E-3</v>
+        <v>1.4652777777777778E-2</v>
       </c>
       <c r="I176" s="1">
-        <v>46146.591087962966</v>
+        <v>46027.668981481482</v>
       </c>
       <c r="J176">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K176" t="s">
         <v>11</v>
@@ -5475,86 +5388,66 @@
     </row>
     <row r="177" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B177" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C177">
-        <v>2827</v>
+        <v>2270</v>
       </c>
       <c r="D177" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H177" s="2">
-        <v>4.8495370370370368E-3</v>
+        <v>2.3148148148148147E-5</v>
       </c>
       <c r="I177" s="1">
-        <v>46146.591087962966</v>
+        <v>46027.669675925928</v>
       </c>
       <c r="J177">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K177" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="178" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B178" t="s">
-        <v>34</v>
-      </c>
-      <c r="C178">
-        <v>2919</v>
-      </c>
-      <c r="D178" t="s">
-        <v>41</v>
-      </c>
-      <c r="F178" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G178" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H178" s="2">
-        <v>8.2523148148148148E-3</v>
-      </c>
-      <c r="I178" s="1">
-        <v>46174.50439814815</v>
-      </c>
-      <c r="J178">
-        <v>0</v>
-      </c>
+      <c r="F178" s="2"/>
+      <c r="G178" s="1"/>
+      <c r="H178" s="2"/>
+      <c r="I178" s="1"/>
       <c r="K178" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C179">
-        <v>3666</v>
+        <v>3874</v>
       </c>
       <c r="D179" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H179" s="2">
-        <v>1.4201388888888888E-2</v>
+        <v>0</v>
       </c>
       <c r="I179" s="1">
-        <v>46174.50509259259</v>
+        <v>46027.670370370368</v>
       </c>
       <c r="J179">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K179" t="s">
         <v>11</v>
@@ -5562,25 +5455,25 @@
     </row>
     <row r="180" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B180" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C180">
-        <v>2828</v>
+        <v>1843</v>
       </c>
       <c r="D180" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H180" s="2">
-        <v>8.5532407407407415E-3</v>
+        <v>7.1064814814814819E-3</v>
       </c>
       <c r="I180" s="1">
-        <v>46174.505787037036</v>
+        <v>46027.671064814815</v>
       </c>
       <c r="J180">
         <v>0</v>
@@ -5591,28 +5484,28 @@
     </row>
     <row r="181" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B181" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C181">
-        <v>4883</v>
+        <v>4745</v>
       </c>
       <c r="D181" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H181" s="2">
-        <v>7.9745370370370369E-3</v>
+        <v>0</v>
       </c>
       <c r="I181" s="1">
-        <v>46174.505787037036</v>
+        <v>46027.671064814815</v>
       </c>
       <c r="J181">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K181" t="s">
         <v>11</v>
@@ -5620,28 +5513,28 @@
     </row>
     <row r="182" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B182" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C182">
-        <v>2830</v>
+        <v>4736</v>
       </c>
       <c r="D182" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H182" s="2">
-        <v>8.711805555555556E-2</v>
+        <v>0</v>
       </c>
       <c r="I182" s="1">
-        <v>46174.506481481483</v>
+        <v>46027.671759259261</v>
       </c>
       <c r="J182">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K182" t="s">
         <v>11</v>
@@ -5649,28 +5542,28 @@
     </row>
     <row r="183" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B183" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C183">
-        <v>2832</v>
+        <v>2008</v>
       </c>
       <c r="D183" t="s">
         <v>39</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H183" s="2">
-        <v>7.4305555555555557E-3</v>
+        <v>1.150462962962963E-2</v>
       </c>
       <c r="I183" s="1">
-        <v>46174.506481481483</v>
+        <v>46027.671759259261</v>
       </c>
       <c r="J183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K183" t="s">
         <v>11</v>
@@ -5678,28 +5571,28 @@
     </row>
     <row r="184" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B184" t="s">
+        <v>30</v>
+      </c>
+      <c r="C184">
+        <v>1840</v>
+      </c>
+      <c r="D184" t="s">
         <v>34</v>
       </c>
-      <c r="C184">
-        <v>2827</v>
-      </c>
-      <c r="D184" t="s">
-        <v>43</v>
-      </c>
       <c r="F184" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H184" s="2">
-        <v>8.8773148148148153E-3</v>
+        <v>1.1226851851851852E-2</v>
       </c>
       <c r="I184" s="1">
-        <v>46175.504282407404</v>
+        <v>46027.672453703701</v>
       </c>
       <c r="J184">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K184" t="s">
         <v>11</v>
@@ -5707,277 +5600,868 @@
     </row>
     <row r="185" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B185" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C185">
-        <v>2826</v>
+        <v>2043</v>
       </c>
       <c r="D185" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H185" s="2">
-        <v>6.8055555555555551E-3</v>
+        <v>3.4722222222222222E-5</v>
       </c>
       <c r="I185" s="1">
-        <v>46176.513194444444</v>
+        <v>46027.673148148147</v>
       </c>
       <c r="J185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K185" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="186" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B186" t="s">
+      <c r="F186" s="2"/>
+      <c r="G186" s="1"/>
+      <c r="H186" s="2"/>
+      <c r="I186" s="1"/>
+      <c r="K186" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="187" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B187" t="s">
+        <v>30</v>
+      </c>
+      <c r="C187">
+        <v>1839</v>
+      </c>
+      <c r="D187" t="s">
+        <v>36</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H187" s="2">
+        <v>7.1643518518518514E-3</v>
+      </c>
+      <c r="I187" s="1">
+        <v>46027.673148148147</v>
+      </c>
+      <c r="J187">
+        <v>3</v>
+      </c>
+      <c r="K187" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="188" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B188" t="s">
+        <v>30</v>
+      </c>
+      <c r="C188">
+        <v>1841</v>
+      </c>
+      <c r="D188" t="s">
+        <v>31</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H188" s="2">
+        <v>1.207175925925926E-2</v>
+      </c>
+      <c r="I188" s="1">
+        <v>46055.710648148146</v>
+      </c>
+      <c r="J188">
+        <v>1</v>
+      </c>
+      <c r="K188" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B189" t="s">
+        <v>30</v>
+      </c>
+      <c r="C189">
+        <v>3874</v>
+      </c>
+      <c r="D189" t="s">
+        <v>49</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H189" s="2">
+        <v>1.1041666666666667E-2</v>
+      </c>
+      <c r="I189" s="1">
+        <v>46055.711342592593</v>
+      </c>
+      <c r="J189">
+        <v>2</v>
+      </c>
+      <c r="K189" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="190" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B190" t="s">
+        <v>30</v>
+      </c>
+      <c r="C190">
+        <v>1843</v>
+      </c>
+      <c r="D190" t="s">
+        <v>33</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H190" s="2">
+        <v>9.2824074074074076E-3</v>
+      </c>
+      <c r="I190" s="1">
+        <v>46055.712037037039</v>
+      </c>
+      <c r="J190">
+        <v>0</v>
+      </c>
+      <c r="K190" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="191" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B191" t="s">
+        <v>30</v>
+      </c>
+      <c r="C191">
+        <v>1840</v>
+      </c>
+      <c r="D191" t="s">
         <v>34</v>
       </c>
-      <c r="C186">
-        <v>2825</v>
-      </c>
-      <c r="D186" t="s">
-        <v>40</v>
-      </c>
-      <c r="F186" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G186" s="1" t="s">
+      <c r="F191" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G191" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H186" s="2">
-        <v>6.3425925925925924E-3</v>
-      </c>
-      <c r="I186" s="1">
-        <v>46176.513888888891</v>
-      </c>
-      <c r="J186">
+      <c r="H191" s="2">
+        <v>1.4791666666666667E-2</v>
+      </c>
+      <c r="I191" s="1">
+        <v>46055.712731481479</v>
+      </c>
+      <c r="J191">
+        <v>1</v>
+      </c>
+      <c r="K191" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="192" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B192" t="s">
+        <v>30</v>
+      </c>
+      <c r="C192">
+        <v>1839</v>
+      </c>
+      <c r="D192" t="s">
+        <v>36</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H192" s="2">
+        <v>8.1481481481481474E-3</v>
+      </c>
+      <c r="I192" s="1">
+        <v>46055.712731481479</v>
+      </c>
+      <c r="J192">
         <v>0</v>
       </c>
-      <c r="K186" t="s">
+      <c r="K192" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="187" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F187" s="2"/>
-      <c r="G187" s="1"/>
-      <c r="H187" s="2"/>
-      <c r="I187" s="1"/>
-    </row>
-    <row r="188" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F188" s="2"/>
-      <c r="G188" s="1"/>
-      <c r="H188" s="2"/>
-      <c r="I188" s="1"/>
-    </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F189" s="2"/>
-      <c r="G189" s="1"/>
-      <c r="H189" s="2"/>
-      <c r="I189" s="1"/>
-    </row>
-    <row r="190" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F190" s="2"/>
-      <c r="G190" s="1"/>
-      <c r="H190" s="2"/>
-      <c r="I190" s="1"/>
-    </row>
-    <row r="191" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F191" s="2"/>
-      <c r="G191" s="1"/>
-      <c r="H191" s="2"/>
-      <c r="I191" s="1"/>
-    </row>
-    <row r="192" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F192" s="2"/>
-      <c r="G192" s="1"/>
-      <c r="H192" s="2"/>
-      <c r="I192" s="1"/>
-    </row>
-    <row r="193" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F193" s="2"/>
-      <c r="G193" s="1"/>
-      <c r="H193" s="2"/>
-      <c r="I193" s="1"/>
-    </row>
-    <row r="194" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F194" s="2"/>
-      <c r="G194" s="1"/>
-      <c r="H194" s="2"/>
-      <c r="I194" s="1"/>
-    </row>
-    <row r="195" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B193" t="s">
+        <v>30</v>
+      </c>
+      <c r="C193">
+        <v>1841</v>
+      </c>
+      <c r="D193" t="s">
+        <v>31</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H193" s="2">
+        <v>1.1655092592592592E-2</v>
+      </c>
+      <c r="I193" s="1">
+        <v>46083.668865740743</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B194" t="s">
+        <v>30</v>
+      </c>
+      <c r="C194">
+        <v>3874</v>
+      </c>
+      <c r="D194" t="s">
+        <v>49</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H194" s="2">
+        <v>4.8032407407407407E-3</v>
+      </c>
+      <c r="I194" s="1">
+        <v>46083.669560185182</v>
+      </c>
+      <c r="J194">
+        <v>5</v>
+      </c>
+      <c r="K194" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="195" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F195" s="2"/>
       <c r="G195" s="1"/>
       <c r="I195" s="1"/>
-    </row>
-    <row r="196" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F196" s="2"/>
-      <c r="G196" s="1"/>
-      <c r="H196" s="2"/>
-      <c r="I196" s="1"/>
-    </row>
-    <row r="197" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F197" s="2"/>
-      <c r="G197" s="1"/>
-      <c r="H197" s="2"/>
-      <c r="I197" s="1"/>
-    </row>
-    <row r="198" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F198" s="2"/>
-      <c r="G198" s="1"/>
-      <c r="H198" s="2"/>
-      <c r="I198" s="1"/>
-    </row>
-    <row r="199" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F199" s="2"/>
-      <c r="G199" s="1"/>
-      <c r="H199" s="2"/>
-      <c r="I199" s="1"/>
-    </row>
-    <row r="200" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F200" s="2"/>
-      <c r="G200" s="1"/>
-      <c r="H200" s="2"/>
-      <c r="I200" s="1"/>
-    </row>
-    <row r="201" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F201" s="2"/>
-      <c r="G201" s="1"/>
-      <c r="H201" s="2"/>
-      <c r="I201" s="1"/>
-    </row>
-    <row r="202" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F202" s="2"/>
-      <c r="G202" s="1"/>
-      <c r="H202" s="2"/>
-      <c r="I202" s="1"/>
-    </row>
-    <row r="203" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F203" s="2"/>
-      <c r="G203" s="1"/>
-      <c r="H203" s="2"/>
-      <c r="I203" s="1"/>
-    </row>
-    <row r="204" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F204" s="2"/>
-      <c r="G204" s="1"/>
-      <c r="H204" s="2"/>
-      <c r="I204" s="1"/>
-    </row>
-    <row r="205" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="K195" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="196" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B196" t="s">
+        <v>30</v>
+      </c>
+      <c r="C196">
+        <v>1843</v>
+      </c>
+      <c r="D196" t="s">
+        <v>33</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H196" s="2">
+        <v>5.6365740740740742E-3</v>
+      </c>
+      <c r="I196" s="1">
+        <v>46083.669560185182</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="197" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B197" t="s">
+        <v>30</v>
+      </c>
+      <c r="C197">
+        <v>1840</v>
+      </c>
+      <c r="D197" t="s">
+        <v>34</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H197" s="2">
+        <v>7.8009259259259256E-3</v>
+      </c>
+      <c r="I197" s="1">
+        <v>46083.670254629629</v>
+      </c>
+      <c r="J197">
+        <v>1</v>
+      </c>
+      <c r="K197" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="198" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B198" t="s">
+        <v>30</v>
+      </c>
+      <c r="C198">
+        <v>1839</v>
+      </c>
+      <c r="D198" t="s">
+        <v>36</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H198" s="2">
+        <v>6.8402777777777776E-3</v>
+      </c>
+      <c r="I198" s="1">
+        <v>46083.670949074076</v>
+      </c>
+      <c r="J198">
+        <v>1</v>
+      </c>
+      <c r="K198" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="199" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B199" t="s">
+        <v>30</v>
+      </c>
+      <c r="C199">
+        <v>1841</v>
+      </c>
+      <c r="D199" t="s">
+        <v>31</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H199" s="2">
+        <v>1.5046296296296295E-2</v>
+      </c>
+      <c r="I199" s="1">
+        <v>46122.585185185184</v>
+      </c>
+      <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="200" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B200" t="s">
+        <v>30</v>
+      </c>
+      <c r="C200">
+        <v>3874</v>
+      </c>
+      <c r="D200" t="s">
+        <v>49</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H200" s="2">
+        <v>6.7013888888888887E-3</v>
+      </c>
+      <c r="I200" s="1">
+        <v>46122.585185185184</v>
+      </c>
+      <c r="J200">
+        <v>4</v>
+      </c>
+      <c r="K200" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="201" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B201" t="s">
+        <v>30</v>
+      </c>
+      <c r="C201">
+        <v>1843</v>
+      </c>
+      <c r="D201" t="s">
+        <v>33</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H201" s="2">
+        <v>1.1111111111111112E-2</v>
+      </c>
+      <c r="I201" s="1">
+        <v>46122.585879629631</v>
+      </c>
+      <c r="J201">
+        <v>1</v>
+      </c>
+      <c r="K201" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="202" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B202" t="s">
+        <v>30</v>
+      </c>
+      <c r="C202">
+        <v>1840</v>
+      </c>
+      <c r="D202" t="s">
+        <v>34</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H202" s="2">
+        <v>0</v>
+      </c>
+      <c r="I202" s="1">
+        <v>46122.585879629631</v>
+      </c>
+      <c r="J202">
+        <v>4</v>
+      </c>
+      <c r="K202" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="203" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B203" t="s">
+        <v>30</v>
+      </c>
+      <c r="C203">
+        <v>1839</v>
+      </c>
+      <c r="D203" t="s">
+        <v>36</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H203" s="2">
+        <v>9.2939814814814812E-3</v>
+      </c>
+      <c r="I203" s="1">
+        <v>46122.586574074077</v>
+      </c>
+      <c r="J203">
+        <v>3</v>
+      </c>
+      <c r="K203" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="204" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B204" t="s">
+        <v>30</v>
+      </c>
+      <c r="C204">
+        <v>1841</v>
+      </c>
+      <c r="D204" t="s">
+        <v>31</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H204" s="2">
+        <v>6.2962962962962964E-3</v>
+      </c>
+      <c r="I204" s="1">
+        <v>46146.584837962961</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="205" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F205" s="2"/>
       <c r="G205" s="1"/>
       <c r="H205" s="2"/>
       <c r="I205" s="1"/>
-    </row>
-    <row r="206" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F206" s="2"/>
-      <c r="G206" s="1"/>
-      <c r="H206" s="2"/>
-      <c r="I206" s="1"/>
-    </row>
-    <row r="207" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F207" s="2"/>
-      <c r="G207" s="1"/>
-      <c r="H207" s="2"/>
-      <c r="I207" s="1"/>
-    </row>
-    <row r="208" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F208" s="2"/>
-      <c r="G208" s="1"/>
-      <c r="H208" s="2"/>
-      <c r="I208" s="1"/>
-    </row>
-    <row r="209" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="K205" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="206" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B206" t="s">
+        <v>30</v>
+      </c>
+      <c r="C206">
+        <v>3874</v>
+      </c>
+      <c r="D206" t="s">
+        <v>49</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H206" s="2">
+        <v>1.1851851851851851E-2</v>
+      </c>
+      <c r="I206" s="1">
+        <v>46146.585532407407</v>
+      </c>
+      <c r="J206">
+        <v>3</v>
+      </c>
+      <c r="K206" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B207" t="s">
+        <v>30</v>
+      </c>
+      <c r="C207">
+        <v>1843</v>
+      </c>
+      <c r="D207" t="s">
+        <v>33</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H207" s="2">
+        <v>8.726851851851852E-3</v>
+      </c>
+      <c r="I207" s="1">
+        <v>46146.586226851854</v>
+      </c>
+      <c r="J207">
+        <v>0</v>
+      </c>
+      <c r="K207" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="208" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B208" t="s">
+        <v>30</v>
+      </c>
+      <c r="C208">
+        <v>1840</v>
+      </c>
+      <c r="D208" t="s">
+        <v>34</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H208" s="2">
+        <v>8.611111111111111E-3</v>
+      </c>
+      <c r="I208" s="1">
+        <v>46146.586226851854</v>
+      </c>
+      <c r="J208">
+        <v>1</v>
+      </c>
+      <c r="K208" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="209" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F209" s="2"/>
       <c r="G209" s="1"/>
       <c r="I209" s="1"/>
-    </row>
-    <row r="210" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F210" s="2"/>
-      <c r="G210" s="1"/>
-      <c r="H210" s="2"/>
-      <c r="I210" s="1"/>
-    </row>
-    <row r="211" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F211" s="2"/>
-      <c r="G211" s="1"/>
-      <c r="H211" s="2"/>
-      <c r="I211" s="1"/>
-    </row>
-    <row r="212" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F212" s="2"/>
-      <c r="G212" s="1"/>
-      <c r="H212" s="2"/>
-      <c r="I212" s="1"/>
-    </row>
-    <row r="213" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F213" s="2"/>
-      <c r="G213" s="1"/>
-      <c r="I213" s="1"/>
-    </row>
-    <row r="214" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="K209" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="210" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B210" t="s">
+        <v>30</v>
+      </c>
+      <c r="C210">
+        <v>1839</v>
+      </c>
+      <c r="D210" t="s">
+        <v>36</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H210" s="2">
+        <v>5.8680555555555552E-3</v>
+      </c>
+      <c r="I210" s="1">
+        <v>46146.586921296293</v>
+      </c>
+      <c r="J210">
+        <v>2</v>
+      </c>
+      <c r="K210" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="211" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B211" t="s">
+        <v>30</v>
+      </c>
+      <c r="C211">
+        <v>1843</v>
+      </c>
+      <c r="D211" t="s">
+        <v>33</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H211" s="2">
+        <v>1.3321759259259259E-2</v>
+      </c>
+      <c r="I211" s="1">
+        <v>46174.503703703704</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B212" t="s">
+        <v>30</v>
+      </c>
+      <c r="C212">
+        <v>1841</v>
+      </c>
+      <c r="D212" t="s">
+        <v>31</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H212" s="2">
+        <v>1.1319444444444444E-2</v>
+      </c>
+      <c r="I212" s="1">
+        <v>46176.513888888891</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="213" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B213" t="s">
+        <v>30</v>
+      </c>
+      <c r="C213">
+        <v>3874</v>
+      </c>
+      <c r="D213" t="s">
+        <v>49</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G213" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H213">
+        <v>0</v>
+      </c>
+      <c r="I213" s="1">
+        <v>46176.51458333333</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="214" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F214" s="2"/>
       <c r="G214" s="1"/>
       <c r="H214" s="2"/>
       <c r="I214" s="1"/>
-    </row>
-    <row r="215" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F215" s="2"/>
-      <c r="G215" s="1"/>
-      <c r="H215" s="2"/>
-      <c r="I215" s="1"/>
-    </row>
-    <row r="216" spans="6:9" x14ac:dyDescent="0.25">
-      <c r="F216" s="2"/>
-      <c r="G216" s="1"/>
-      <c r="H216" s="2"/>
-      <c r="I216" s="1"/>
-    </row>
-    <row r="217" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="K214" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="215" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B215" t="s">
+        <v>30</v>
+      </c>
+      <c r="C215">
+        <v>1840</v>
+      </c>
+      <c r="D215" t="s">
+        <v>34</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H215" s="2">
+        <v>4.7199074074074074E-2</v>
+      </c>
+      <c r="I215" s="1">
+        <v>46176.51458333333</v>
+      </c>
+      <c r="J215">
+        <v>1</v>
+      </c>
+      <c r="K215" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="216" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B216" t="s">
+        <v>30</v>
+      </c>
+      <c r="C216">
+        <v>1839</v>
+      </c>
+      <c r="D216" t="s">
+        <v>36</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G216" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H216" s="2">
+        <v>0</v>
+      </c>
+      <c r="I216" s="1">
+        <v>46176.515277777777</v>
+      </c>
+      <c r="J216">
+        <v>2</v>
+      </c>
+      <c r="K216" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="217" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F217" s="2"/>
       <c r="G217" s="1"/>
       <c r="I217" s="1"/>
     </row>
-    <row r="218" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F218" s="2"/>
       <c r="G218" s="1"/>
       <c r="H218" s="2"/>
       <c r="I218" s="1"/>
     </row>
-    <row r="219" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F219" s="2"/>
       <c r="G219" s="1"/>
       <c r="H219" s="2"/>
       <c r="I219" s="1"/>
     </row>
-    <row r="220" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F220" s="2"/>
       <c r="G220" s="1"/>
       <c r="I220" s="1"/>
     </row>
-    <row r="221" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F221" s="2"/>
       <c r="G221" s="1"/>
       <c r="I221" s="1"/>
     </row>
-    <row r="222" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F222" s="2"/>
       <c r="G222" s="1"/>
       <c r="H222" s="2"/>
       <c r="I222" s="1"/>
     </row>
-    <row r="223" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F223" s="2"/>
       <c r="G223" s="1"/>
     </row>
-    <row r="224" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F224" s="2"/>
       <c r="G224" s="1"/>
       <c r="I224" s="1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Agra-Trucking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4CACD4-6456-4D22-AE2C-761E9CEACB25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F9EFCB-2342-43BC-8E1F-5656988A4270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -31131,5 +31131,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Agra-Trucking\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmull\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4DA0C82-033C-4F5D-8559-BBCBED923335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{412D194A-8147-4861-8A4C-E51658582830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -592,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K7400"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -607,39 +607,39 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>16</v>
       </c>
@@ -668,7 +668,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>16</v>
       </c>
@@ -697,7 +697,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -726,7 +726,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H5" s="2"/>
       <c r="I5" s="1"/>
       <c r="J5" s="2"/>
@@ -734,7 +734,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>16</v>
       </c>
@@ -763,7 +763,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>16</v>
       </c>
@@ -792,7 +792,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>16</v>
       </c>
@@ -821,7 +821,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H9" s="2"/>
       <c r="I9" s="1"/>
       <c r="J9" s="2"/>
@@ -829,7 +829,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -858,7 +858,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>16</v>
       </c>
@@ -887,7 +887,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>16</v>
       </c>
@@ -916,7 +916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>16</v>
       </c>
@@ -945,7 +945,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>16</v>
       </c>
@@ -974,7 +974,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>16</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>16</v>
       </c>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmull\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Agra-Trucking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{412D194A-8147-4861-8A4C-E51658582830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A15EAF-DEF0-4844-8725-4A9CF6D0A63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6753,10 +6753,10 @@
         <v>58</v>
       </c>
       <c r="G229" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H229" s="2">
-        <v>0</v>
+        <v>6.122685185185185E-3</v>
       </c>
       <c r="I229" s="1">
         <v>46237.628009259257</v>
@@ -6840,10 +6840,10 @@
         <v>58</v>
       </c>
       <c r="G232" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H232" s="2">
-        <v>0</v>
+        <v>8.7384259259259255E-3</v>
       </c>
       <c r="I232" s="1">
         <v>46237.62939814815</v>
@@ -6898,10 +6898,10 @@
         <v>58</v>
       </c>
       <c r="G234" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H234" s="2">
-        <v>0</v>
+        <v>9.6412037037037039E-3</v>
       </c>
       <c r="I234" s="1">
         <v>46237.630787037036</v>
